--- a/output/yearly_surface_area_iteration_95_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_95_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.844976213814</v>
+        <v>10.84497666826905</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907152934372</v>
+        <v>37.78907311288193</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.13141532364883</v>
+        <v>7.609526455617027</v>
       </c>
       <c r="C2" t="n">
-        <v>3.767947688899258</v>
+        <v>5.16497467204247</v>
       </c>
       <c r="D2" t="n">
-        <v>38.16740549800325</v>
+        <v>25.04536568304038</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.15942834318226</v>
+        <v>19.81657741022187</v>
       </c>
       <c r="C3" t="n">
-        <v>25.53034904893831</v>
+        <v>18.16233252856599</v>
       </c>
       <c r="D3" t="n">
-        <v>85.55931242510952</v>
+        <v>60.33330516448773</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.02236887968198</v>
+        <v>34.93156506480576</v>
       </c>
       <c r="C4" t="n">
-        <v>62.48627787990099</v>
+        <v>54.34366242087795</v>
       </c>
       <c r="D4" t="n">
-        <v>99.29396280752239</v>
+        <v>70.92243590249383</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.71356032120075</v>
+        <v>42.87783098297945</v>
       </c>
       <c r="C5" t="n">
-        <v>89.24086631603508</v>
+        <v>98.27294519510575</v>
       </c>
       <c r="D5" t="n">
-        <v>71.79030087304803</v>
+        <v>57.30952223540757</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.80009298789471</v>
+        <v>41.78121879733577</v>
       </c>
       <c r="C6" t="n">
-        <v>82.95866275655973</v>
+        <v>132.669457761097</v>
       </c>
       <c r="D6" t="n">
-        <v>49.10702016642546</v>
+        <v>44.84034464376883</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.09922293805371</v>
+        <v>30.3625112492411</v>
       </c>
       <c r="C7" t="n">
-        <v>71.2051792413169</v>
+        <v>123.8455093953266</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>38.86640986342697</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.68971097219578</v>
+        <v>15.85522542358599</v>
       </c>
       <c r="C8" t="n">
-        <v>48.65050748395068</v>
+        <v>78.10784734987622</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>36.21667280966483</v>
       </c>
     </row>
     <row r="9">
@@ -878,10 +878,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.098436812331936</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>32.28280975874785</v>
+        <v>40.93593402397924</v>
       </c>
       <c r="D9" t="n">
         <v>34.39062207976576</v>
@@ -895,10 +895,10 @@
         <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>29.67528785626833</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -926,7 +926,7 @@
         <v>27.98864530037232</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>26.27647730416588</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1010,7 +1010,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.708069888001105</v>
+        <v>7.69327237556999</v>
       </c>
       <c r="C21" t="n">
-        <v>96.35087360001381</v>
+        <v>94.24258660073237</v>
       </c>
       <c r="D21" t="n">
-        <v>8.671578624001244</v>
+        <v>8.654931422516238</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.842200661523521</v>
+        <v>7.179520961156924</v>
       </c>
       <c r="C2" t="n">
-        <v>5.683337459884785</v>
+        <v>11.04466167277662</v>
       </c>
       <c r="D2" t="n">
-        <v>43.12326790904114</v>
+        <v>24.57118154188917</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.70920705756047</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="C3" t="n">
-        <v>19.69385894719102</v>
+        <v>19.07535789351553</v>
       </c>
       <c r="D3" t="n">
-        <v>94.12506114466295</v>
+        <v>65.099690268606</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.66952054322987</v>
+        <v>35.99087083768807</v>
       </c>
       <c r="C4" t="n">
-        <v>63.08612572719579</v>
+        <v>49.72355772469245</v>
       </c>
       <c r="D4" t="n">
-        <v>115.4132783635508</v>
+        <v>82.1025787584565</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.56754195517523</v>
+        <v>47.22206457427158</v>
       </c>
       <c r="C5" t="n">
-        <v>101.0709261522092</v>
+        <v>98.19931411728723</v>
       </c>
       <c r="D5" t="n">
-        <v>89.04451677518571</v>
+        <v>68.45235867860886</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56.99634471775284</v>
+        <v>49.91205328390785</v>
       </c>
       <c r="C6" t="n">
-        <v>111.3360801478138</v>
+        <v>144.4631929322139</v>
       </c>
       <c r="D6" t="n">
-        <v>58.48565598509524</v>
+        <v>51.32086123950202</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>42.04040019125691</v>
+        <v>39.46527596301753</v>
       </c>
       <c r="C7" t="n">
-        <v>93.96209102575797</v>
+        <v>155.7051858935441</v>
       </c>
       <c r="D7" t="n">
-        <v>44.31609136970101</v>
+        <v>42.81892612072463</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>25.11801501315464</v>
+        <v>23.78283813537898</v>
       </c>
       <c r="C8" t="n">
-        <v>70.93127163183205</v>
+        <v>119.6652276706437</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>38.05254101660637</v>
       </c>
     </row>
     <row r="9">
@@ -1189,10 +1189,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.31406145436774</v>
+        <v>11.75937400146829</v>
       </c>
       <c r="C9" t="n">
-        <v>45.5953086283346</v>
+        <v>67.00624431025328</v>
       </c>
       <c r="D9" t="n">
         <v>36.0546844384641</v>
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.690610604442014</v>
+        <v>6.548257187326225</v>
       </c>
       <c r="C10" t="n">
-        <v>34.30717352490479</v>
+        <v>39.43189654107314</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>35.3036474447153</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>32.16303653882975</v>
+        <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>37.13853390395258</v>
       </c>
     </row>
     <row r="12">
@@ -1237,7 +1237,7 @@
         <v>31.02617269731195</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.61794557879453</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>26.42668470291564</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1321,7 +1321,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1349,7 +1349,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.893236387477377</v>
+        <v>7.877005365077618</v>
       </c>
       <c r="C21" t="n">
-        <v>105.5720366825099</v>
+        <v>103.3856954166437</v>
       </c>
       <c r="D21" t="n">
-        <v>9.866545484346721</v>
+        <v>9.846256706347022</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.265734832681396</v>
+        <v>8.939794594871456</v>
       </c>
       <c r="C2" t="n">
-        <v>6.631705742187204</v>
+        <v>11.11436575977814</v>
       </c>
       <c r="D2" t="n">
-        <v>43.70838954077225</v>
+        <v>21.61710269981052</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.55351008321273</v>
+        <v>22.92871763268426</v>
       </c>
       <c r="C3" t="n">
-        <v>20.700150344044</v>
+        <v>30.65016332658542</v>
       </c>
       <c r="D3" t="n">
-        <v>103.50075172022</v>
+        <v>68.22164796811084</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.06967269593508</v>
+        <v>38.81143199198916</v>
       </c>
       <c r="C4" t="n">
-        <v>56.41122308602172</v>
+        <v>48.15374314560181</v>
       </c>
       <c r="D4" t="n">
-        <v>131.7623228823729</v>
+        <v>92.98917905084939</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>63.02820261264524</v>
+        <v>49.72552122010096</v>
       </c>
       <c r="C5" t="n">
-        <v>106.7405191442345</v>
+        <v>94.10051745205679</v>
       </c>
       <c r="D5" t="n">
-        <v>104.6052178874977</v>
+        <v>78.58890372495718</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>66.69699378341556</v>
+        <v>55.70829172978102</v>
       </c>
       <c r="C6" t="n">
-        <v>133.2732325992088</v>
+        <v>150.1386764104647</v>
       </c>
       <c r="D6" t="n">
-        <v>70.3196428120863</v>
+        <v>59.41144407019999</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>53.05953642372311</v>
+        <v>48.02906118716245</v>
       </c>
       <c r="C7" t="n">
-        <v>122.4681173662684</v>
+        <v>178.4620976779852</v>
       </c>
       <c r="D7" t="n">
-        <v>49.28667999630262</v>
+        <v>46.53189593818607</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>33.88011327355743</v>
+        <v>31.96079651175491</v>
       </c>
       <c r="C8" t="n">
-        <v>94.29686699290613</v>
+        <v>157.4674230226671</v>
       </c>
       <c r="D8" t="n">
-        <v>41.30703465618455</v>
+        <v>40.55599766243574</v>
       </c>
     </row>
     <row r="9">
@@ -1500,10 +1500,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17.9718734739421</v>
+        <v>17.08437354930299</v>
       </c>
       <c r="C9" t="n">
-        <v>64.5656195174957</v>
+        <v>103.0609287487174</v>
       </c>
       <c r="D9" t="n">
         <v>37.16405934426299</v>
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>42.84837855185204</v>
+        <v>56.22959976073607</v>
       </c>
       <c r="D10" t="n">
-        <v>36.44247478164161</v>
+        <v>36.30012136452581</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>5.508586368528851</v>
       </c>
       <c r="C11" t="n">
-        <v>35.89465956267188</v>
+        <v>38.56010457970196</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>37.13853390395258</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>33.41280136633594</v>
+        <v>33.62976760897449</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>35.79943003535993</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>30.95941385342317</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>28.5776939229204</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>31.65056423721292</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1590,7 +1590,7 @@
         <v>25.083653843506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>22.31905230834699</v>
+        <v>21.90573652485908</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1632,7 +1632,7 @@
         <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1660,7 +1660,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.062725169496066</v>
+        <v>8.045697886898189</v>
       </c>
       <c r="C21" t="n">
-        <v>113.8859930191319</v>
+        <v>111.6340581807124</v>
       </c>
       <c r="D21" t="n">
-        <v>11.08624710805709</v>
+        <v>11.06283459448501</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.469537444537233</v>
+        <v>8.137706720501811</v>
       </c>
       <c r="C2" t="n">
-        <v>4.456152829576273</v>
+        <v>7.468154786205487</v>
       </c>
       <c r="D2" t="n">
-        <v>35.76114187489431</v>
+        <v>17.81675733667111</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>30.12983704333461</v>
+        <v>27.36621725587984</v>
       </c>
       <c r="C3" t="n">
-        <v>32.65292864324891</v>
+        <v>43.82521751757761</v>
       </c>
       <c r="D3" t="n">
-        <v>110.4662516818511</v>
+        <v>73.51326809400116</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.27317220815464</v>
+        <v>23.89181213055038</v>
       </c>
       <c r="C4" t="n">
-        <v>85.2294451964826</v>
+        <v>74.24074314284805</v>
       </c>
       <c r="D4" t="n">
-        <v>124.3471824721968</v>
+        <v>89.44114284770141</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.57639338004667</v>
+        <v>31.3668391506856</v>
       </c>
       <c r="C5" t="n">
-        <v>79.61973881441634</v>
+        <v>89.70719647555231</v>
       </c>
       <c r="D5" t="n">
-        <v>71.12762117268143</v>
+        <v>57.35860962061991</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.92585450502953</v>
+        <v>29.82647700272235</v>
       </c>
       <c r="C6" t="n">
-        <v>80.66431837173494</v>
+        <v>117.5348351524282</v>
       </c>
       <c r="D6" t="n">
-        <v>32.4428346345401</v>
+        <v>30.63151012020474</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.45747873464579</v>
+        <v>21.13997331554657</v>
       </c>
       <c r="C7" t="n">
-        <v>66.29447722467437</v>
+        <v>110.7303418142935</v>
       </c>
       <c r="D7" t="n">
-        <v>29.04500583014188</v>
+        <v>28.50602634051038</v>
       </c>
     </row>
     <row r="8">
@@ -1797,10 +1797,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.43383467428585</v>
+        <v>11.849694790259</v>
       </c>
       <c r="C8" t="n">
-        <v>47.56567627075796</v>
+        <v>75.93818492349078</v>
       </c>
       <c r="D8" t="n">
         <v>27.37112599440107</v>
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.323436963053704</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>32.61562223048752</v>
+        <v>42.93280885441725</v>
       </c>
       <c r="D9" t="n">
-        <v>27.73437264497238</v>
+        <v>27.62343515439249</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>28.04362317181014</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>28.75539025738908</v>
+        <v>29.04009709162065</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>28.60910984945629</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
-        <v>27.12078032981814</v>
+        <v>26.90381408717959</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -1887,7 +1887,7 @@
         <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>23.96838845148163</v>
+        <v>23.66110142005238</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.63357142660446</v>
+        <v>18.27523351455437</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.57528845915541</v>
       </c>
     </row>
     <row r="16">
@@ -1929,7 +1929,7 @@
         <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>18.41660518396592</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
         <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
-        <v>9.628981483252716</v>
+        <v>9.027170140549421</v>
       </c>
     </row>
     <row r="20">
@@ -1968,7 +1968,7 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>74.64718669240621</v>
       </c>
       <c r="D20" t="n">
         <v>7.397468951499714</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.230751768227005</v>
+        <v>4.960771149559132</v>
       </c>
       <c r="C2" t="n">
-        <v>2.04988920646734</v>
+        <v>3.999640147101506</v>
       </c>
       <c r="D2" t="n">
-        <v>24.71255321130071</v>
+        <v>12.58502382073986</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>30.57162351024567</v>
+        <v>28.50013585428491</v>
       </c>
       <c r="C3" t="n">
-        <v>25.25545969174919</v>
+        <v>36.98734475749858</v>
       </c>
       <c r="D3" t="n">
-        <v>113.3967685790278</v>
+        <v>71.39269305282805</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.43604451606838</v>
+        <v>36.27165068110266</v>
       </c>
       <c r="C4" t="n">
-        <v>85.75271672284615</v>
+        <v>93.49968785705774</v>
       </c>
       <c r="D4" t="n">
-        <v>147.9582147593325</v>
+        <v>104.0544574254152</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.7551125199486</v>
+        <v>35.09748042682348</v>
       </c>
       <c r="C5" t="n">
-        <v>117.3679380427062</v>
+        <v>114.5454133929966</v>
       </c>
       <c r="D5" t="n">
-        <v>91.2779928023472</v>
+        <v>71.00490270965058</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.88939097125216</v>
+        <v>35.62271544859552</v>
       </c>
       <c r="C6" t="n">
-        <v>103.2857489729899</v>
+        <v>135.1650604252924</v>
       </c>
       <c r="D6" t="n">
-        <v>41.05668899160162</v>
+        <v>37.23278168356029</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.13997331554657</v>
+        <v>19.94224111636546</v>
       </c>
       <c r="C7" t="n">
-        <v>86.17683173108075</v>
+        <v>136.9606769763598</v>
       </c>
       <c r="D7" t="n">
-        <v>31.73990327829938</v>
+        <v>31.08115056874977</v>
       </c>
     </row>
     <row r="8">
@@ -2108,10 +2108,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>9.930378028456486</v>
       </c>
       <c r="C8" t="n">
-        <v>62.66986470059513</v>
+        <v>100.8058542720625</v>
       </c>
       <c r="D8" t="n">
         <v>28.53940576245478</v>
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>37.94062177832222</v>
+        <v>49.25624581747095</v>
       </c>
       <c r="D9" t="n">
-        <v>28.73281006019139</v>
+        <v>28.6218725696115</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>32.88363935374691</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -2167,10 +2167,10 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>21.47965802121596</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2184,7 +2184,7 @@
         <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.36435157146258</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>18.74450891718435</v>
       </c>
     </row>
     <row r="15">
@@ -2226,7 +2226,7 @@
         <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>15.70599977254047</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>12.27773678931061</v>
+        <v>11.8055161435679</v>
       </c>
     </row>
     <row r="18">
@@ -2254,7 +2254,7 @@
         <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
-        <v>8.025787482217675</v>
+        <v>7.490734983403163</v>
       </c>
     </row>
     <row r="19">
@@ -2265,7 +2265,7 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>64.99562501195582</v>
       </c>
       <c r="D19" t="n">
         <v>6.018113427032947</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.570837384523903</v>
+        <v>5.351506735849362</v>
       </c>
       <c r="C2" t="n">
-        <v>3.679590395517045</v>
+        <v>5.950372835439918</v>
       </c>
       <c r="D2" t="n">
-        <v>24.89417653658637</v>
+        <v>13.87111331330318</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.31298189567226</v>
+        <v>22.81090790817464</v>
       </c>
       <c r="C3" t="n">
-        <v>15.98285262513807</v>
+        <v>25.52053157189584</v>
       </c>
       <c r="D3" t="n">
-        <v>107.0546784095934</v>
+        <v>65.25676990128549</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50.13196476965913</v>
+        <v>45.05240214788613</v>
       </c>
       <c r="C4" t="n">
-        <v>73.93443785912304</v>
+        <v>92.87431456945251</v>
       </c>
       <c r="D4" t="n">
-        <v>168.8380249332537</v>
+        <v>114.9793458782737</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.69530802544756</v>
+        <v>44.17864669110647</v>
       </c>
       <c r="C5" t="n">
-        <v>137.7392029058275</v>
+        <v>143.4824269756714</v>
       </c>
       <c r="D5" t="n">
-        <v>120.0186568441726</v>
+        <v>89.90354601640168</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.66425195181016</v>
+        <v>41.70071548558752</v>
       </c>
       <c r="C6" t="n">
-        <v>144.3424379645916</v>
+        <v>159.3965572615122</v>
       </c>
       <c r="D6" t="n">
-        <v>57.15735134124931</v>
+        <v>48.86551023118075</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.73990327829938</v>
+        <v>29.04500583014188</v>
       </c>
       <c r="C7" t="n">
-        <v>116.719002810199</v>
+        <v>166.4847756861741</v>
       </c>
       <c r="D7" t="n">
-        <v>35.69241953559704</v>
+        <v>34.31502750653876</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.27108553955913</v>
+        <v>14.52004854581032</v>
       </c>
       <c r="C8" t="n">
-        <v>86.86994561027902</v>
+        <v>138.7749467338079</v>
       </c>
       <c r="D8" t="n">
-        <v>30.62561963397925</v>
+        <v>30.54217107911827</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.767186925373262</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>55.57968278052466</v>
+        <v>82.09374302911826</v>
       </c>
       <c r="D9" t="n">
-        <v>29.50937249425062</v>
+        <v>29.39843500367073</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.847068342315751</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>38.00836236991527</v>
+        <v>44.12955930589413</v>
       </c>
       <c r="D10" t="n">
-        <v>30.60598467989432</v>
+        <v>30.7483380970101</v>
       </c>
     </row>
     <row r="11">
@@ -2464,7 +2464,7 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
         <v>30.03068052520567</v>
@@ -2478,10 +2478,10 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>26.4698816019025</v>
+        <v>26.03594911662541</v>
       </c>
       <c r="D12" t="n">
-        <v>29.07347651356504</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.77239876353076</v>
+        <v>19.51223562190536</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>19.97365704290136</v>
+        <v>19.66637001147211</v>
       </c>
     </row>
     <row r="15">
@@ -2537,7 +2537,7 @@
         <v>14.87936820556466</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>6.955682484588652</v>
       </c>
     </row>
     <row r="19">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.856304982281471</v>
+        <v>3.133738671955819</v>
       </c>
       <c r="C2" t="n">
-        <v>1.690569546713007</v>
+        <v>2.755765805820797</v>
       </c>
       <c r="D2" t="n">
-        <v>17.17960307661494</v>
+        <v>9.576948854927636</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.49107914076843</v>
+        <v>22.93853510972673</v>
       </c>
       <c r="C3" t="n">
-        <v>16.30192062901829</v>
+        <v>26.15866757965627</v>
       </c>
       <c r="D3" t="n">
-        <v>106.4312686173967</v>
+        <v>64.14739499548659</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>55.59440899608838</v>
+        <v>49.99157484795184</v>
       </c>
       <c r="C4" t="n">
-        <v>68.61238355440109</v>
+        <v>90.94714382601602</v>
       </c>
       <c r="D4" t="n">
-        <v>182.3154574171539</v>
+        <v>122.2413336465873</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.51154127830416</v>
+        <v>45.9703362513569</v>
       </c>
       <c r="C5" t="n">
-        <v>157.8159434576748</v>
+        <v>171.3395180836746</v>
       </c>
       <c r="D5" t="n">
-        <v>131.0878622095554</v>
+        <v>98.00296457643788</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.92964262712628</v>
+        <v>35.34095385747668</v>
       </c>
       <c r="C6" t="n">
-        <v>174.7726898054257</v>
+        <v>199.7287164473796</v>
       </c>
       <c r="D6" t="n">
-        <v>56.03030497677397</v>
+        <v>48.02022545782425</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.12083708308037</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>120.4319726276605</v>
+        <v>178.9411905576576</v>
       </c>
       <c r="D7" t="n">
-        <v>35.81219275551515</v>
+        <v>34.7941203862112</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.673119072214817</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>68.17746932141974</v>
+        <v>103.9768993567797</v>
       </c>
       <c r="D8" t="n">
-        <v>32.04424506661589</v>
+        <v>32.21114217633784</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>28.95468504135117</v>
+        <v>33.61405964570653</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>32.06093477758807</v>
       </c>
     </row>
     <row r="10">
@@ -2761,7 +2761,7 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>26.05067533218912</v>
+        <v>26.47773558353648</v>
       </c>
       <c r="D10" t="n">
         <v>23.48831382410494</v>
@@ -2775,10 +2775,10 @@
         <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>21.14586380177204</v>
+        <v>20.7904711328347</v>
       </c>
       <c r="D11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.05550195525234</v>
+        <v>15.83853571261379</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>20.61179305066178</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -2834,7 +2834,7 @@
         <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
-        <v>12.90016483380309</v>
+        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.919578803709772</v>
+        <v>9.506263020221864</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>30.22212132753381</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.66664774891259</v>
       </c>
     </row>
     <row r="18">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.767366851822511</v>
+        <v>3.399792299806704</v>
       </c>
       <c r="C2" t="n">
-        <v>1.655226629360122</v>
+        <v>6.76522342996477</v>
       </c>
       <c r="D2" t="n">
-        <v>15.06197327855456</v>
+        <v>12.16090881250524</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.50732688338412</v>
+        <v>16.98914402199105</v>
       </c>
       <c r="C3" t="n">
-        <v>11.27046364475338</v>
+        <v>17.92671307954676</v>
       </c>
       <c r="D3" t="n">
-        <v>96.48616437337652</v>
+        <v>57.62368150076654</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>52.41649167744146</v>
+        <v>47.15825097349554</v>
       </c>
       <c r="C4" t="n">
-        <v>54.58615410382691</v>
+        <v>78.69493247701583</v>
       </c>
       <c r="D4" t="n">
-        <v>192.1682773769749</v>
+        <v>125.7893698497353</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>67.44606728175589</v>
+        <v>58.75760009917161</v>
       </c>
       <c r="C5" t="n">
-        <v>144.1205629834318</v>
+        <v>171.0449937724006</v>
       </c>
       <c r="D5" t="n">
-        <v>160.8102739556276</v>
+        <v>116.0671223345792</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.81646390369741</v>
+        <v>46.49066253460771</v>
       </c>
       <c r="C6" t="n">
-        <v>211.1199350597554</v>
+        <v>234.9086636813599</v>
       </c>
       <c r="D6" t="n">
-        <v>78.69198723390311</v>
+        <v>64.08063615159783</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.63713856452295</v>
+        <v>20.48122060599696</v>
       </c>
       <c r="C7" t="n">
-        <v>180.1988093667978</v>
+        <v>230.9826546120768</v>
       </c>
       <c r="D7" t="n">
-        <v>41.50142070162541</v>
+        <v>39.1059563032632</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.425538724295373</v>
+        <v>6.258641614573416</v>
       </c>
       <c r="C8" t="n">
-        <v>106.56380455747</v>
+        <v>160.0543282233575</v>
       </c>
       <c r="D8" t="n">
-        <v>34.13045893814036</v>
+        <v>34.04701038327938</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>50.25468323268996</v>
+        <v>69.33593161243097</v>
       </c>
       <c r="D9" t="n">
-        <v>33.50312215512664</v>
+        <v>33.05937219280708</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.423534171157875</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>32.17187226816798</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>25.0542014123786</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>24.6997904911455</v>
+        <v>24.52209415667683</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.44213062427633</v>
+        <v>18.22516438163779</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.60978849752428</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3145,7 +3145,7 @@
         <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>8.266315669758143</v>
       </c>
     </row>
     <row r="17">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.94432778496098</v>
+        <v>34.47210713921825</v>
       </c>
       <c r="D17" t="n">
         <v>4.722206457427158</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.32125248346696</v>
+        <v>2.439643045053324</v>
       </c>
       <c r="C2" t="n">
-        <v>1.403899217072939</v>
+        <v>3.410591524553419</v>
       </c>
       <c r="D2" t="n">
-        <v>11.75152001983432</v>
+        <v>9.648616437337651</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.32922963828795</v>
+        <v>14.87838645786041</v>
       </c>
       <c r="C3" t="n">
-        <v>9.100801218367932</v>
+        <v>22.25622045527519</v>
       </c>
       <c r="D3" t="n">
-        <v>88.69599634017808</v>
+        <v>54.86987919035423</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.32416633551325</v>
+        <v>42.60195987808609</v>
       </c>
       <c r="C4" t="n">
-        <v>44.33768981919445</v>
+        <v>65.31960175435728</v>
       </c>
       <c r="D4" t="n">
-        <v>196.0481443041583</v>
+        <v>126.4019804171853</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>74.19558274845271</v>
+        <v>64.45173678380311</v>
       </c>
       <c r="C5" t="n">
-        <v>131.9959788359837</v>
+        <v>166.6762164885023</v>
       </c>
       <c r="D5" t="n">
-        <v>183.0468594568178</v>
+        <v>129.2470852640926</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>64.48315271033901</v>
+        <v>55.8692983532775</v>
       </c>
       <c r="C6" t="n">
-        <v>227.9451272151372</v>
+        <v>259.2206638293279</v>
       </c>
       <c r="D6" t="n">
-        <v>95.27566945404023</v>
+        <v>75.47185476397357</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.25974653546468</v>
+        <v>19.28348840681585</v>
       </c>
       <c r="C7" t="n">
-        <v>226.5510454751067</v>
+        <v>276.9156844506723</v>
       </c>
       <c r="D7" t="n">
-        <v>47.19064864773568</v>
+        <v>43.59745205019235</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.257258956241669</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C8" t="n">
-        <v>141.0280577150543</v>
+        <v>203.0303339767616</v>
       </c>
       <c r="D8" t="n">
-        <v>36.13322425480386</v>
+        <v>35.88287859022092</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>60.90468232835936</v>
+        <v>82.87030546317747</v>
       </c>
       <c r="D9" t="n">
-        <v>33.17030968338697</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>25.48126166372597</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.52209415667683</v>
+        <v>24.34439782220815</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.7912318963607</v>
+        <v>17.57426565372215</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3442,7 +3442,7 @@
         <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>7.525096153051802</v>
+        <v>6.808420328951629</v>
       </c>
     </row>
     <row r="16">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>3.719842051391165</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.536656141324511</v>
+        <v>4.541564879845745</v>
       </c>
       <c r="C2" t="n">
-        <v>7.222717860143783</v>
+        <v>13.27322896141688</v>
       </c>
       <c r="D2" t="n">
-        <v>17.12167996206437</v>
+        <v>13.57168026350791</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.88329519638165</v>
+        <v>11.69261515757951</v>
       </c>
       <c r="C3" t="n">
-        <v>7.299294181075036</v>
+        <v>18.02488784997144</v>
       </c>
       <c r="D3" t="n">
-        <v>79.89462817160543</v>
+        <v>50.94779711188823</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.22358610132357</v>
+        <v>36.14402347955058</v>
       </c>
       <c r="C4" t="n">
-        <v>34.28066633689012</v>
+        <v>60.73778521863742</v>
       </c>
       <c r="D4" t="n">
-        <v>193.1765322692364</v>
+        <v>123.6835210241259</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>73.75379628154164</v>
+        <v>64.20629985774141</v>
       </c>
       <c r="C5" t="n">
-        <v>109.4894127161256</v>
+        <v>146.2558642401686</v>
       </c>
       <c r="D5" t="n">
-        <v>205.4061634210389</v>
+        <v>141.6907374154209</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>78.24921901928779</v>
+        <v>67.90454345963914</v>
       </c>
       <c r="C6" t="n">
-        <v>221.3036039959076</v>
+        <v>262.5212996110056</v>
       </c>
       <c r="D6" t="n">
-        <v>121.5600007398401</v>
+        <v>92.82031844571895</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>40.24380189248525</v>
+        <v>35.45287309576081</v>
       </c>
       <c r="C7" t="n">
-        <v>272.7835083634975</v>
+        <v>318.3572185423387</v>
       </c>
       <c r="D7" t="n">
-        <v>58.74876436983337</v>
+        <v>51.86180422454201</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>10.09727513817844</v>
       </c>
       <c r="C8" t="n">
-        <v>204.2820622996763</v>
+        <v>271.2078032981814</v>
       </c>
       <c r="D8" t="n">
-        <v>39.22082078466007</v>
+        <v>38.38633523605029</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.884374755077128</v>
+        <v>2.662499773917349</v>
       </c>
       <c r="C9" t="n">
-        <v>104.8359285979956</v>
+        <v>145.8828001125547</v>
       </c>
       <c r="D9" t="n">
-        <v>34.39062207976576</v>
+        <v>34.05780960802609</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>46.40721397974673</v>
+        <v>55.66018609227292</v>
       </c>
       <c r="D10" t="n">
-        <v>26.76244241776806</v>
+        <v>27.04714925199963</v>
       </c>
     </row>
     <row r="11">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>20.82875929330033</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61179305066178</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3753,7 +3753,7 @@
         <v>11.98419422574081</v>
       </c>
       <c r="D14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.67690719431156</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
-        <v>7.166758241001715</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.363688618927824</v>
+        <v>6.151631114810514</v>
       </c>
       <c r="C2" t="n">
-        <v>3.615776794741003</v>
+        <v>5.976880023454582</v>
       </c>
       <c r="D2" t="n">
-        <v>9.42772320388212</v>
+        <v>10.18955942237764</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.215223731408304</v>
+        <v>3.212278488295564</v>
       </c>
       <c r="C2" t="n">
-        <v>4.043818793792612</v>
+        <v>7.433793616556848</v>
       </c>
       <c r="D2" t="n">
-        <v>12.60171353171206</v>
+        <v>9.988301143007048</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.71840263979719</v>
+        <v>16.52281386247382</v>
       </c>
       <c r="C3" t="n">
-        <v>14.82929907264807</v>
+        <v>31.1508546557513</v>
       </c>
       <c r="D3" t="n">
-        <v>86.45270283597412</v>
+        <v>56.44558425567036</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>56.48779940695297</v>
+        <v>49.00884539600077</v>
       </c>
       <c r="C4" t="n">
-        <v>52.03361007278519</v>
+        <v>86.33980184998573</v>
       </c>
       <c r="D4" t="n">
-        <v>198.9197563390802</v>
+        <v>127.3974725892916</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.80482179996669</v>
+        <v>40.61981126321179</v>
       </c>
       <c r="C5" t="n">
-        <v>175.6592079823606</v>
+        <v>220.7950586851077</v>
       </c>
       <c r="D5" t="n">
-        <v>186.1639084178015</v>
+        <v>131.0878622095554</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24.95602664195392</v>
+        <v>22.01765576314322</v>
       </c>
       <c r="C6" t="n">
-        <v>227.3816040328995</v>
+        <v>263.6885976313551</v>
       </c>
       <c r="D6" t="n">
-        <v>92.82031844571895</v>
+        <v>75.19009317285472</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.186393195086651</v>
+        <v>6.647413705455153</v>
       </c>
       <c r="C7" t="n">
-        <v>143.667977291774</v>
+        <v>190.7388527195915</v>
       </c>
       <c r="D7" t="n">
-        <v>35.63253292563798</v>
+        <v>33.59638818703009</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.002765316663493</v>
+        <v>1.835868206941535</v>
       </c>
       <c r="C8" t="n">
-        <v>77.27336180126643</v>
+        <v>107.4817386609408</v>
       </c>
       <c r="D8" t="n">
-        <v>25.2849121228766</v>
+        <v>25.03456645829366</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5546874528994477</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>35.38905949498476</v>
+        <v>42.48905889209769</v>
       </c>
       <c r="D9" t="n">
-        <v>20.41249826669968</v>
+        <v>20.63437324785945</v>
       </c>
     </row>
     <row r="10">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.8811517745239</v>
+        <v>16.70345544005523</v>
       </c>
       <c r="D11" t="n">
-        <v>16.52575910558656</v>
+        <v>16.34806277111788</v>
       </c>
     </row>
     <row r="12">
@@ -4361,7 +4361,7 @@
         <v>9.886199381765381</v>
       </c>
       <c r="D13" t="n">
-        <v>9.886199381765381</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>5.838453597155781</v>
+        <v>5.223879534297279</v>
       </c>
     </row>
     <row r="15">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
         <v>2.5083653843506</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.763259934556276</v>
+        <v>6.770132168486005</v>
       </c>
       <c r="C2" t="n">
-        <v>3.815071578703105</v>
+        <v>8.217228284545802</v>
       </c>
       <c r="D2" t="n">
-        <v>19.50438164027138</v>
+        <v>13.01208407208722</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.51375714895735</v>
+        <v>13.06706194352505</v>
       </c>
       <c r="C3" t="n">
-        <v>9.1106186954104</v>
+        <v>15.06000978314607</v>
       </c>
       <c r="D3" t="n">
-        <v>11.05447914981909</v>
+        <v>11.69752389610075</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4557,7 +4557,7 @@
         <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.35114688295087</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39867071670253</v>
+        <v>13.3981705161729</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14598198744264</v>
+        <v>70.14336329055224</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576314201965003</v>
+        <v>1.576255354843871</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.118832529942869</v>
+        <v>4.4168829214064</v>
       </c>
       <c r="C2" t="n">
-        <v>4.483641765295182</v>
+        <v>8.598146393793566</v>
       </c>
       <c r="D2" t="n">
-        <v>23.65226569071415</v>
+        <v>17.63807925449819</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.43860454408685</v>
+        <v>19.26188995732242</v>
       </c>
       <c r="C3" t="n">
-        <v>12.87071240267569</v>
+        <v>25.68742868161779</v>
       </c>
       <c r="D3" t="n">
-        <v>24.76458583962579</v>
+        <v>19.79694245613693</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>15.68538307075129</v>
+        <v>15.18763698469816</v>
       </c>
       <c r="C4" t="n">
-        <v>14.42187377538565</v>
+        <v>23.49616780573891</v>
       </c>
       <c r="D4" t="n">
-        <v>20.86704745376596</v>
+        <v>21.19887817780138</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.424156065963628</v>
       </c>
       <c r="D5" t="n">
         <v>29.10881943091793</v>
@@ -4882,7 +4882,7 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
         <v>34.77743067523902</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.4428389917061</v>
+        <v>15.44149869328681</v>
       </c>
       <c r="C21" t="n">
-        <v>86.15478595372879</v>
+        <v>86.14730849938958</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251123998253917</v>
+        <v>3.250841830165644</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.240569245269474</v>
+        <v>5.147303213366026</v>
       </c>
       <c r="C2" t="n">
-        <v>4.265693774952391</v>
+        <v>4.710425484976196</v>
       </c>
       <c r="D2" t="n">
-        <v>18.58252054598363</v>
+        <v>17.53401399784803</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.47649179392497</v>
+        <v>17.02350519163969</v>
       </c>
       <c r="C3" t="n">
-        <v>15.64414966717292</v>
+        <v>30.39981766200248</v>
       </c>
       <c r="D3" t="n">
-        <v>37.93964003061799</v>
+        <v>29.31007771028852</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.03969618099315</v>
+        <v>27.75891633757857</v>
       </c>
       <c r="C4" t="n">
-        <v>24.90006702281185</v>
+        <v>47.51560713784138</v>
       </c>
       <c r="D4" t="n">
-        <v>28.58849314766712</v>
+        <v>26.35501712050563</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>13.84264262988003</v>
+        <v>13.2045066221196</v>
       </c>
       <c r="C5" t="n">
-        <v>17.45056544298706</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D5" t="n">
-        <v>29.94330497952772</v>
+        <v>30.06602344255857</v>
       </c>
     </row>
     <row r="6">
@@ -5190,10 +5190,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>12.11574841810989</v>
       </c>
       <c r="D6" t="n">
         <v>36.6290068454485</v>
@@ -5204,7 +5204,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
@@ -5218,7 +5218,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
         <v>29.87458264023044</v>
@@ -5232,10 +5232,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>29.50937249425062</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
         <v>41.26874649571891</v>
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>29.46715734296802</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5280,7 +5280,7 @@
         <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>46.2138096820101</v>
       </c>
     </row>
     <row r="13">
@@ -5291,10 +5291,10 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>45.52854978444583</v>
+        <v>45.00822350119503</v>
       </c>
     </row>
     <row r="14">
@@ -5305,7 +5305,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73918826724955</v>
+        <v>16.73498751016044</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1090484302222</v>
+        <v>102.0834238119787</v>
       </c>
       <c r="D21" t="n">
-        <v>5.021756480174863</v>
+        <v>5.020496253048133</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.892449720889356</v>
+        <v>5.200317589395354</v>
       </c>
       <c r="C2" t="n">
-        <v>5.66664774891259</v>
+        <v>6.997897635871265</v>
       </c>
       <c r="D2" t="n">
-        <v>30.19954113033613</v>
+        <v>14.59269787592459</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.1917849596934</v>
+        <v>17.36220814960484</v>
       </c>
       <c r="C3" t="n">
-        <v>16.17920216598743</v>
+        <v>23.39013905368026</v>
       </c>
       <c r="D3" t="n">
-        <v>43.62395923820702</v>
+        <v>36.11358930071892</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.13652935081509</v>
+        <v>30.71986741358695</v>
       </c>
       <c r="C4" t="n">
-        <v>33.00439432136928</v>
+        <v>63.46900733185205</v>
       </c>
       <c r="D4" t="n">
-        <v>40.21533120906209</v>
+        <v>34.63802250123597</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.27433388230815</v>
+        <v>27.29258617806133</v>
       </c>
       <c r="C5" t="n">
-        <v>33.13398501832986</v>
+        <v>59.56754195517523</v>
       </c>
       <c r="D5" t="n">
-        <v>33.57577148524092</v>
+        <v>32.42221793275092</v>
       </c>
     </row>
     <row r="6">
@@ -5501,10 +5501,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.31700669748049</v>
+        <v>11.99499345048753</v>
       </c>
       <c r="C6" t="n">
-        <v>20.28683456055609</v>
+        <v>28.37741739125406</v>
       </c>
       <c r="D6" t="n">
         <v>38.27932473628739</v>
@@ -5515,7 +5515,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
         <v>21.19985992550562</v>
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>31.54355373745002</v>
       </c>
       <c r="D8" t="n">
         <v>40.38910055271378</v>
@@ -5543,10 +5543,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>34.39062207976576</v>
       </c>
       <c r="D9" t="n">
         <v>41.93437143919824</v>
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>10.10709261522091</v>
       </c>
       <c r="C10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5574,10 +5574,10 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>50.82115165804038</v>
       </c>
     </row>
     <row r="12">
@@ -5591,7 +5591,7 @@
         <v>34.49763257952867</v>
       </c>
       <c r="D12" t="n">
-        <v>47.29864089520282</v>
+        <v>47.08167465256428</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
-        <v>46.30903920932205</v>
+        <v>45.78871292607123</v>
       </c>
     </row>
     <row r="14">
@@ -5616,7 +5616,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5630,7 +5630,7 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
         <v>43.71722527011046</v>
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.77765165941727</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>39.00483628972577</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.0719691845333</v>
+        <v>18.06091733259217</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8980846800506</v>
+        <v>117.8259845031013</v>
       </c>
       <c r="D21" t="n">
-        <v>6.88455968934602</v>
+        <v>6.88034946003511</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.565748719553421</v>
+        <v>5.685300955293279</v>
       </c>
       <c r="C2" t="n">
-        <v>8.805295159389642</v>
+        <v>5.345616249623882</v>
       </c>
       <c r="D2" t="n">
-        <v>28.57573042751191</v>
+        <v>16.6062624173348</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.29348581030757</v>
+        <v>15.67851083682156</v>
       </c>
       <c r="C3" t="n">
-        <v>18.42740440871263</v>
+        <v>24.01354884587698</v>
       </c>
       <c r="D3" t="n">
-        <v>53.50034114292993</v>
+        <v>36.85480881742526</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.8234907018806</v>
+        <v>23.39406604449724</v>
       </c>
       <c r="C4" t="n">
-        <v>31.23037621979529</v>
+        <v>50.31064285183204</v>
       </c>
       <c r="D4" t="n">
-        <v>45.33318199130072</v>
+        <v>38.70933023074748</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.48831382410494</v>
+        <v>22.70291566070749</v>
       </c>
       <c r="C5" t="n">
-        <v>35.7356164345839</v>
+        <v>67.74059159302993</v>
       </c>
       <c r="D5" t="n">
-        <v>32.86400439966199</v>
+        <v>29.99239236474006</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.92707293244525</v>
+        <v>13.28304643845935</v>
       </c>
       <c r="C6" t="n">
-        <v>25.43904651244335</v>
+        <v>42.62650357069227</v>
       </c>
       <c r="D6" t="n">
-        <v>30.99377502307181</v>
+        <v>31.03402667894593</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.928774385946488</v>
+        <v>5.689227946110266</v>
       </c>
       <c r="C7" t="n">
-        <v>16.40893112878119</v>
+        <v>20.00212772632452</v>
       </c>
       <c r="D7" t="n">
-        <v>31.14103717870882</v>
+        <v>30.72183090899544</v>
       </c>
     </row>
     <row r="8">
@@ -5843,7 +5843,7 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
         <v>30.37527396939631</v>
@@ -5857,7 +5857,7 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>22.18749811597791</v>
+        <v>21.96562313481813</v>
       </c>
       <c r="D9" t="n">
         <v>29.95312245657017</v>
@@ -5868,10 +5868,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.6377194015997</v>
       </c>
       <c r="D10" t="n">
         <v>33.73775985644164</v>
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>34.47308888692249</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>32.11100391050467</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>30.17892442854696</v>
       </c>
     </row>
     <row r="14">
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -5969,10 +5969,10 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.066374452467975</v>
+        <v>7.059263391868861</v>
       </c>
       <c r="C21" t="n">
-        <v>67.13055729844577</v>
+        <v>66.18059429877057</v>
       </c>
       <c r="D21" t="n">
-        <v>5.299780839350981</v>
+        <v>5.294447543901646</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.628179661997716</v>
+        <v>5.587126184868598</v>
       </c>
       <c r="C2" t="n">
-        <v>6.33423618780042</v>
+        <v>5.421210822850886</v>
       </c>
       <c r="D2" t="n">
-        <v>30.0395162545439</v>
+        <v>23.71313404837746</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.27509464583413</v>
+        <v>18.32922963828795</v>
       </c>
       <c r="C3" t="n">
-        <v>28.90756115154733</v>
+        <v>21.98133109808609</v>
       </c>
       <c r="D3" t="n">
-        <v>65.20768251607315</v>
+        <v>42.21024254409161</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.83473189498382</v>
+        <v>28.16732338254523</v>
       </c>
       <c r="C4" t="n">
-        <v>40.82794177651211</v>
+        <v>56.70476564959152</v>
       </c>
       <c r="D4" t="n">
-        <v>63.74978717526663</v>
+        <v>49.58316780298516</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.98043146583985</v>
+        <v>30.01693605734623</v>
       </c>
       <c r="C5" t="n">
-        <v>49.1119289049467</v>
+        <v>83.59581701661591</v>
       </c>
       <c r="D5" t="n">
-        <v>42.80419990516094</v>
+        <v>38.01817984695774</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24.35225180384214</v>
+        <v>23.54721868635975</v>
       </c>
       <c r="C6" t="n">
-        <v>44.51833139677587</v>
+        <v>81.50960314509145</v>
       </c>
       <c r="D6" t="n">
-        <v>34.61642405174254</v>
+        <v>33.77113927838603</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.27675504160636</v>
+        <v>11.49822911213864</v>
       </c>
       <c r="C7" t="n">
-        <v>28.7455727803466</v>
+        <v>44.6155244194963</v>
       </c>
       <c r="D7" t="n">
-        <v>33.71616140694821</v>
+        <v>33.41672835715293</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.00829594999048</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>20.86213871524472</v>
+        <v>23.61594102565702</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>32.3780392860598</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
         <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>31.17343485294896</v>
       </c>
     </row>
     <row r="10">
@@ -6179,10 +6179,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.91184799526281</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
         <v>34.16482010778901</v>
@@ -6199,7 +6199,7 @@
         <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>34.82848155585983</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
-        <v>33.41280136633594</v>
+        <v>32.97886888105885</v>
       </c>
     </row>
     <row r="13">
@@ -6224,10 +6224,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>30.95941385342317</v>
       </c>
     </row>
     <row r="14">
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6305,7 +6305,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.293176706765946</v>
+        <v>7.283440484470058</v>
       </c>
       <c r="C21" t="n">
-        <v>77.49000250938818</v>
+        <v>75.56569502637686</v>
       </c>
       <c r="D21" t="n">
-        <v>6.381529618420203</v>
+        <v>6.373010423911301</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.08192702780899</v>
+        <v>5.987679248201297</v>
       </c>
       <c r="C2" t="n">
-        <v>6.326382206166446</v>
+        <v>4.046764036905352</v>
       </c>
       <c r="D2" t="n">
-        <v>36.75761579470483</v>
+        <v>26.81742028920587</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.02122290106171</v>
+        <v>19.13426275577033</v>
       </c>
       <c r="C3" t="n">
-        <v>26.30102099677205</v>
+        <v>21.44136986075034</v>
       </c>
       <c r="D3" t="n">
-        <v>74.10722545507048</v>
+        <v>51.38467484027806</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.64475586644545</v>
+        <v>32.36625831360885</v>
       </c>
       <c r="C4" t="n">
-        <v>59.74229304653115</v>
+        <v>55.22429011158733</v>
       </c>
       <c r="D4" t="n">
-        <v>81.50273091116171</v>
+        <v>59.14244519923635</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.90804417763285</v>
+        <v>37.11006322052944</v>
       </c>
       <c r="C5" t="n">
-        <v>64.45173678380311</v>
+        <v>96.01492547533807</v>
       </c>
       <c r="D5" t="n">
-        <v>56.81864838328416</v>
+        <v>47.86020058203201</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.13969557810609</v>
+        <v>32.88560284915541</v>
       </c>
       <c r="C6" t="n">
-        <v>62.91333813124836</v>
+        <v>110.4102920627091</v>
       </c>
       <c r="D6" t="n">
-        <v>40.6139207769863</v>
+        <v>38.48058301565798</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.37951975538279</v>
+        <v>20.60099382591507</v>
       </c>
       <c r="C7" t="n">
-        <v>48.92736033654828</v>
+        <v>85.15875936177682</v>
       </c>
       <c r="D7" t="n">
-        <v>36.17151241526948</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.09727513817844</v>
+        <v>9.429686699290613</v>
       </c>
       <c r="C8" t="n">
-        <v>30.79251674370121</v>
+        <v>42.97600575340412</v>
       </c>
       <c r="D8" t="n">
-        <v>34.38080460272329</v>
+        <v>34.54770171244525</v>
       </c>
     </row>
     <row r="9">
@@ -6479,7 +6479,7 @@
         <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>27.29062268265283</v>
       </c>
       <c r="D9" t="n">
         <v>32.72655972106742</v>
@@ -6493,10 +6493,10 @@
         <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>34.30717352490479</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>33.62976760897449</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -6549,7 +6549,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
         <v>30.42141611149592</v>
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6608,7 +6608,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
         <v>19.50241814486288</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.507800260950929</v>
+        <v>7.495211126501036</v>
       </c>
       <c r="C21" t="n">
-        <v>87.27817803355454</v>
+        <v>85.25802656394929</v>
       </c>
       <c r="D21" t="n">
-        <v>7.507800260950929</v>
+        <v>7.495211126501036</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_95_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_95_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497666826905</v>
+        <v>10.84497649924665</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907311288193</v>
+        <v>37.78907252392726</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.609526455617027</v>
+        <v>3.950552761889165</v>
       </c>
       <c r="C2" t="n">
-        <v>5.16497467204247</v>
+        <v>8.251589454194441</v>
       </c>
       <c r="D2" t="n">
-        <v>25.04536568304038</v>
+        <v>22.39366513386975</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.81657741022187</v>
+        <v>14.06353586333556</v>
       </c>
       <c r="C3" t="n">
-        <v>18.16233252856599</v>
+        <v>42.07770660401829</v>
       </c>
       <c r="D3" t="n">
-        <v>60.33330516448773</v>
+        <v>59.61662934038756</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.93156506480576</v>
+        <v>34.29342905704534</v>
       </c>
       <c r="C4" t="n">
-        <v>54.34366242087795</v>
+        <v>80.69867954138357</v>
       </c>
       <c r="D4" t="n">
-        <v>70.92243590249383</v>
+        <v>73.51326809400116</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.87783098297945</v>
+        <v>43.61414176116455</v>
       </c>
       <c r="C5" t="n">
-        <v>98.27294519510575</v>
+        <v>110.9129468872834</v>
       </c>
       <c r="D5" t="n">
-        <v>57.30952223540757</v>
+        <v>55.14967728606459</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.78121879733577</v>
+        <v>37.15227837181205</v>
       </c>
       <c r="C6" t="n">
-        <v>132.669457761097</v>
+        <v>125.5046630155038</v>
       </c>
       <c r="D6" t="n">
-        <v>44.84034464376883</v>
+        <v>42.22398701195107</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.3625112492411</v>
+        <v>25.09248957284423</v>
       </c>
       <c r="C7" t="n">
-        <v>123.8455093953266</v>
+        <v>109.1732899553581</v>
       </c>
       <c r="D7" t="n">
-        <v>38.86640986342697</v>
+        <v>38.26754376383641</v>
       </c>
     </row>
     <row r="8">
@@ -864,10 +864,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.85522542358599</v>
+        <v>13.01797455831271</v>
       </c>
       <c r="C8" t="n">
-        <v>78.10784734987622</v>
+        <v>68.17746932141974</v>
       </c>
       <c r="D8" t="n">
         <v>36.21667280966483</v>
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.876561831172157</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>40.93593402397924</v>
+        <v>37.60780930658255</v>
       </c>
       <c r="D9" t="n">
-        <v>34.39062207976576</v>
+        <v>34.27968458918587</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>30.32127784566274</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.852984190737</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -926,7 +926,7 @@
         <v>27.98864530037232</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -937,7 +937,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
         <v>32.5203927031756</v>
@@ -948,7 +948,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
         <v>23.66110142005238</v>
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.69215749368978</v>
       </c>
     </row>
     <row r="17">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.69327237556999</v>
+        <v>7.709819374689451</v>
       </c>
       <c r="C21" t="n">
-        <v>94.24258660073237</v>
+        <v>96.37274218361814</v>
       </c>
       <c r="D21" t="n">
-        <v>8.654931422516238</v>
+        <v>8.673546796525633</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.179520961156924</v>
+        <v>5.539020547360504</v>
       </c>
       <c r="C2" t="n">
-        <v>11.04466167277662</v>
+        <v>8.595201150680824</v>
       </c>
       <c r="D2" t="n">
-        <v>24.57118154188917</v>
+        <v>21.37657451227005</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.57528845915541</v>
+        <v>13.58247948825462</v>
       </c>
       <c r="C3" t="n">
-        <v>19.07535789351553</v>
+        <v>36.62409810692726</v>
       </c>
       <c r="D3" t="n">
-        <v>65.099690268606</v>
+        <v>62.72876956284995</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.99087083768807</v>
+        <v>30.31146036862027</v>
       </c>
       <c r="C4" t="n">
-        <v>49.72355772469245</v>
+        <v>93.06575537178064</v>
       </c>
       <c r="D4" t="n">
-        <v>82.1025787584565</v>
+        <v>83.86383413987529</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.22206457427158</v>
+        <v>47.61476365597031</v>
       </c>
       <c r="C5" t="n">
-        <v>98.19931411728723</v>
+        <v>128.3635123302705</v>
       </c>
       <c r="D5" t="n">
-        <v>68.45235867860886</v>
+        <v>67.54424205218056</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.91205328390785</v>
+        <v>47.05418571684538</v>
       </c>
       <c r="C6" t="n">
-        <v>144.4631929322139</v>
+        <v>150.219179722213</v>
       </c>
       <c r="D6" t="n">
-        <v>51.32086123950202</v>
+        <v>48.62400029593603</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>39.46527596301753</v>
+        <v>33.95570784678443</v>
       </c>
       <c r="C7" t="n">
-        <v>155.7051858935441</v>
+        <v>143.0092245822244</v>
       </c>
       <c r="D7" t="n">
-        <v>42.81892612072463</v>
+        <v>41.68108053150257</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23.78283813537898</v>
+        <v>19.61041039233004</v>
       </c>
       <c r="C8" t="n">
-        <v>119.6652276706437</v>
+        <v>105.1451791248334</v>
       </c>
       <c r="D8" t="n">
-        <v>38.05254101660637</v>
+        <v>37.96909246174539</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.75937400146829</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>67.00624431025328</v>
+        <v>59.46249495082079</v>
       </c>
       <c r="D9" t="n">
-        <v>36.0546844384641</v>
+        <v>35.94374694788421</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.548257187326225</v>
+        <v>6.121196935978863</v>
       </c>
       <c r="C10" t="n">
-        <v>39.43189654107314</v>
+        <v>37.29659528433633</v>
       </c>
       <c r="D10" t="n">
-        <v>35.3036474447153</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>32.51842920776709</v>
+        <v>32.69612554223576</v>
       </c>
       <c r="D11" t="n">
-        <v>37.13853390395258</v>
+        <v>36.78314123501524</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>31.02617269731195</v>
+        <v>30.8092064546734</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -1248,7 +1248,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.09761929554372</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
         <v>32.780555844801</v>
@@ -1259,10 +1259,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
         <v>31.03599017435442</v>
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.69215749368978</v>
       </c>
     </row>
     <row r="17">
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1349,7 +1349,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.877005365077618</v>
+        <v>7.893343092237959</v>
       </c>
       <c r="C21" t="n">
-        <v>103.3856954166437</v>
+        <v>105.5734638586827</v>
       </c>
       <c r="D21" t="n">
-        <v>9.846256706347022</v>
+        <v>9.866678865297448</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.939794594871456</v>
+        <v>6.701409829188727</v>
       </c>
       <c r="C2" t="n">
-        <v>11.11436575977814</v>
+        <v>9.951976477949916</v>
       </c>
       <c r="D2" t="n">
-        <v>21.61710269981052</v>
+        <v>19.69091370407828</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.92871763268426</v>
+        <v>15.59015354343935</v>
       </c>
       <c r="C3" t="n">
-        <v>30.65016332658542</v>
+        <v>34.7980473770282</v>
       </c>
       <c r="D3" t="n">
-        <v>68.22164796811084</v>
+        <v>64.26520471999621</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.81143199198916</v>
+        <v>27.69510273680252</v>
       </c>
       <c r="C4" t="n">
-        <v>48.15374314560181</v>
+        <v>91.17687278880977</v>
       </c>
       <c r="D4" t="n">
-        <v>92.98917905084939</v>
+        <v>93.47416241674732</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.72552122010096</v>
+        <v>46.51029748869265</v>
       </c>
       <c r="C5" t="n">
-        <v>94.10051745205679</v>
+        <v>147.5566799482956</v>
       </c>
       <c r="D5" t="n">
-        <v>78.58890372495718</v>
+        <v>78.3189231062893</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.70829172978102</v>
+        <v>54.21898046243861</v>
       </c>
       <c r="C6" t="n">
-        <v>150.1386764104647</v>
+        <v>172.2770871412303</v>
       </c>
       <c r="D6" t="n">
-        <v>59.41144407019999</v>
+        <v>56.91584140600459</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>48.02906118716245</v>
+        <v>43.29801900039708</v>
       </c>
       <c r="C7" t="n">
-        <v>178.4620976779852</v>
+        <v>174.6293546406056</v>
       </c>
       <c r="D7" t="n">
-        <v>46.53189593818607</v>
+        <v>45.03473068920969</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>31.96079651175491</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="C8" t="n">
-        <v>157.4674230226671</v>
+        <v>142.8639259219958</v>
       </c>
       <c r="D8" t="n">
-        <v>40.55599766243574</v>
+        <v>40.3056519978528</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17.08437354930299</v>
+        <v>13.97812381306608</v>
       </c>
       <c r="C9" t="n">
-        <v>103.0609287487174</v>
+        <v>89.52655489797087</v>
       </c>
       <c r="D9" t="n">
-        <v>37.16405934426299</v>
+        <v>37.05312185368311</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.541205026947251</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>56.22959976073607</v>
+        <v>51.67429041303087</v>
       </c>
       <c r="D10" t="n">
-        <v>36.30012136452581</v>
+        <v>36.44247478164161</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.508586368528851</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>38.56010457970196</v>
+        <v>37.13853390395258</v>
       </c>
       <c r="D11" t="n">
-        <v>37.13853390395258</v>
+        <v>36.78314123501524</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>33.62976760897449</v>
+        <v>33.41280136633594</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>36.01639627799849</v>
       </c>
     </row>
     <row r="13">
@@ -1559,7 +1559,7 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>30.69925071179776</v>
+        <v>30.95941385342317</v>
       </c>
       <c r="D13" t="n">
         <v>33.04071898642641</v>
@@ -1570,10 +1570,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
         <v>31.34327720578367</v>
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.69215749368978</v>
       </c>
     </row>
     <row r="17">
@@ -1646,7 +1646,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1660,7 +1660,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.045697886898189</v>
+        <v>8.060567289548368</v>
       </c>
       <c r="C21" t="n">
-        <v>111.6340581807124</v>
+        <v>113.8555129648707</v>
       </c>
       <c r="D21" t="n">
-        <v>11.06283459448501</v>
+        <v>11.083280023129</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.137706720501811</v>
+        <v>6.032839642596649</v>
       </c>
       <c r="C2" t="n">
-        <v>7.468154786205487</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="D2" t="n">
-        <v>17.81675733667111</v>
+        <v>16.24596100987622</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.36621725587984</v>
+        <v>19.03608798534566</v>
       </c>
       <c r="C3" t="n">
-        <v>43.82521751757761</v>
+        <v>53.51506735849363</v>
       </c>
       <c r="D3" t="n">
-        <v>73.51326809400116</v>
+        <v>69.92498023497907</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.89181213055038</v>
+        <v>22.33476027161494</v>
       </c>
       <c r="C4" t="n">
-        <v>74.24074314284805</v>
+        <v>124.423758793128</v>
       </c>
       <c r="D4" t="n">
-        <v>89.44114284770141</v>
+        <v>90.06651613530664</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.3668391506856</v>
+        <v>30.53235360207581</v>
       </c>
       <c r="C5" t="n">
-        <v>89.70719647555231</v>
+        <v>102.9362467902781</v>
       </c>
       <c r="D5" t="n">
-        <v>57.35860962061991</v>
+        <v>55.0515025156399</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.82647700272235</v>
+        <v>26.88810612391165</v>
       </c>
       <c r="C6" t="n">
-        <v>117.5348351524282</v>
+        <v>114.9989808323586</v>
       </c>
       <c r="D6" t="n">
-        <v>30.63151012020474</v>
+        <v>29.62521872335175</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.13997331554657</v>
+        <v>17.96598298771663</v>
       </c>
       <c r="C7" t="n">
-        <v>110.7303418142935</v>
+        <v>100.429844901336</v>
       </c>
       <c r="D7" t="n">
-        <v>28.50602634051038</v>
+        <v>28.32636651063322</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.849694790259</v>
+        <v>9.680032363873551</v>
       </c>
       <c r="C8" t="n">
-        <v>75.93818492349078</v>
+        <v>65.92435834017331</v>
       </c>
       <c r="D8" t="n">
-        <v>27.37112599440107</v>
+        <v>27.28767743954009</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.101561981893925</v>
+        <v>5.324999547834698</v>
       </c>
       <c r="C9" t="n">
-        <v>42.93280885441725</v>
+        <v>39.38280915586078</v>
       </c>
       <c r="D9" t="n">
-        <v>27.62343515439249</v>
+        <v>27.73437264497238</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.98589567924205</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>29.04009709162065</v>
       </c>
       <c r="D10" t="n">
-        <v>29.04009709162065</v>
+        <v>28.75539025738908</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>28.60910984945629</v>
+        <v>28.78680618392497</v>
       </c>
     </row>
     <row r="12">
@@ -1856,7 +1856,7 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>25.16808414607123</v>
       </c>
       <c r="D12" t="n">
         <v>26.90381408717959</v>
@@ -1867,10 +1867,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
         <v>25.75615102091507</v>
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.89551813718911</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>24.27567548291088</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>23.29196428325557</v>
       </c>
     </row>
     <row r="16">
@@ -1943,7 +1943,7 @@
         <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
         <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>9.628981483252716</v>
       </c>
     </row>
     <row r="20">
@@ -1968,7 +1968,7 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>74.64718669240621</v>
+        <v>75.31968386981528</v>
       </c>
       <c r="D20" t="n">
         <v>7.397468951499714</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.960771149559132</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C2" t="n">
-        <v>3.999640147101506</v>
+        <v>3.262347621212151</v>
       </c>
       <c r="D2" t="n">
-        <v>12.58502382073986</v>
+        <v>12.10004045484194</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>28.50013585428491</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="C3" t="n">
-        <v>36.98734475749858</v>
+        <v>40.2761995667254</v>
       </c>
       <c r="D3" t="n">
-        <v>71.39269305282805</v>
+        <v>67.43134106619218</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.27165068110266</v>
+        <v>29.02242563294421</v>
       </c>
       <c r="C4" t="n">
-        <v>93.49968785705774</v>
+        <v>133.5235782637917</v>
       </c>
       <c r="D4" t="n">
-        <v>104.0544574254152</v>
+        <v>103.1483042943954</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.09748042682348</v>
+        <v>33.40396563699773</v>
       </c>
       <c r="C5" t="n">
-        <v>114.5454133929966</v>
+        <v>161.0066234964769</v>
       </c>
       <c r="D5" t="n">
-        <v>71.00490270965058</v>
+        <v>69.1641257641878</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.62271544859552</v>
+        <v>32.52333794628834</v>
       </c>
       <c r="C6" t="n">
-        <v>135.1650604252924</v>
+        <v>141.0820538387879</v>
       </c>
       <c r="D6" t="n">
-        <v>37.23278168356029</v>
+        <v>35.94472869558847</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.94224111636546</v>
+        <v>16.88802400845363</v>
       </c>
       <c r="C7" t="n">
-        <v>136.9606769763598</v>
+        <v>128.6364381920511</v>
       </c>
       <c r="D7" t="n">
-        <v>31.08115056874977</v>
+        <v>30.78171751895449</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.930378028456486</v>
+        <v>8.261406931236909</v>
       </c>
       <c r="C8" t="n">
-        <v>100.8058542720625</v>
+        <v>87.2871883845839</v>
       </c>
       <c r="D8" t="n">
-        <v>28.53940576245478</v>
+        <v>28.45595720759379</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>4.548437113775471</v>
       </c>
       <c r="C9" t="n">
-        <v>49.25624581747095</v>
+        <v>45.48437113775471</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6218725696115</v>
+        <v>28.73281006019139</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>32.88363935374691</v>
+        <v>31.8871654339364</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2156,7 +2156,7 @@
         <v>29.852984190737</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2164,10 +2164,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
         <v>28.42257778564941</v>
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>17.17076734727672</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2240,7 +2240,7 @@
         <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>12.27773678931061</v>
       </c>
     </row>
     <row r="18">
@@ -2254,7 +2254,7 @@
         <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>8.025787482217675</v>
       </c>
     </row>
     <row r="19">
@@ -2265,7 +2265,7 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>64.99562501195582</v>
+        <v>65.59743635465912</v>
       </c>
       <c r="D19" t="n">
         <v>6.018113427032947</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.351506735849362</v>
+        <v>3.282964323001334</v>
       </c>
       <c r="C2" t="n">
-        <v>5.950372835439918</v>
+        <v>4.265693774952391</v>
       </c>
       <c r="D2" t="n">
-        <v>13.87111331330318</v>
+        <v>16.18214740910017</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.81090790817464</v>
+        <v>16.43936530761284</v>
       </c>
       <c r="C3" t="n">
-        <v>25.52053157189584</v>
+        <v>25.34381698513141</v>
       </c>
       <c r="D3" t="n">
-        <v>65.25676990128549</v>
+        <v>62.43915399009714</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.05240214788613</v>
+        <v>34.089225534562</v>
       </c>
       <c r="C4" t="n">
-        <v>92.87431456945251</v>
+        <v>117.6467543907123</v>
       </c>
       <c r="D4" t="n">
-        <v>114.9793458782737</v>
+        <v>111.7886658394716</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.17864669110647</v>
+        <v>38.28816046562561</v>
       </c>
       <c r="C5" t="n">
-        <v>143.4824269756714</v>
+        <v>202.7063572343602</v>
       </c>
       <c r="D5" t="n">
-        <v>89.90354601640168</v>
+        <v>86.22199212547613</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.70071548558752</v>
+        <v>38.31957639216151</v>
       </c>
       <c r="C6" t="n">
-        <v>159.3965572615122</v>
+        <v>196.5488356333242</v>
       </c>
       <c r="D6" t="n">
-        <v>48.86551023118075</v>
+        <v>47.69821221083129</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.04500583014188</v>
+        <v>25.81112889235289</v>
       </c>
       <c r="C7" t="n">
-        <v>166.4847756861741</v>
+        <v>163.6102184081394</v>
       </c>
       <c r="D7" t="n">
-        <v>34.31502750653876</v>
+        <v>33.53650157707104</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.52004854581032</v>
+        <v>12.01659189998096</v>
       </c>
       <c r="C8" t="n">
-        <v>138.7749467338079</v>
+        <v>125.9238692852171</v>
       </c>
       <c r="D8" t="n">
-        <v>30.54217107911827</v>
+        <v>29.95803119509142</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.656249434793372</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>82.09374302911826</v>
+        <v>73.21874378272709</v>
       </c>
       <c r="D9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.50937249425062</v>
       </c>
     </row>
     <row r="10">
@@ -2450,7 +2450,7 @@
         <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>44.12955930589413</v>
+        <v>41.14013754646259</v>
       </c>
       <c r="D10" t="n">
         <v>30.7483380970101</v>
@@ -2467,7 +2467,7 @@
         <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2475,10 +2475,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>26.03594911662541</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
         <v>28.8565102709265</v>
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.51223562190536</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>26.27647730416588</v>
       </c>
     </row>
     <row r="14">
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
         <v>19.66637001147211</v>
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>11.8055161435679</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>7.490734983403163</v>
       </c>
     </row>
     <row r="19">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.133738671955819</v>
+        <v>1.956623174563893</v>
       </c>
       <c r="C2" t="n">
-        <v>2.755765805820797</v>
+        <v>2.036144738607885</v>
       </c>
       <c r="D2" t="n">
-        <v>9.576948854927636</v>
+        <v>11.28028112179585</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.93853510972673</v>
+        <v>15.85031668506475</v>
       </c>
       <c r="C3" t="n">
-        <v>26.15866757965627</v>
+        <v>23.2232419439583</v>
       </c>
       <c r="D3" t="n">
-        <v>64.14739499548659</v>
+        <v>62.95948027334795</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49.99157484795184</v>
+        <v>37.81593981988289</v>
       </c>
       <c r="C4" t="n">
-        <v>90.94714382601602</v>
+        <v>109.5934779727757</v>
       </c>
       <c r="D4" t="n">
-        <v>122.2413336465873</v>
+        <v>118.5529075217321</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.9703362513569</v>
+        <v>40.37437433715008</v>
       </c>
       <c r="C5" t="n">
-        <v>171.3395180836746</v>
+        <v>236.5766530308752</v>
       </c>
       <c r="D5" t="n">
-        <v>98.00296457643788</v>
+        <v>91.25344910974104</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.34095385747668</v>
+        <v>31.5975498611836</v>
       </c>
       <c r="C6" t="n">
-        <v>199.7287164473796</v>
+        <v>236.5992332280728</v>
       </c>
       <c r="D6" t="n">
-        <v>48.02022545782425</v>
+        <v>47.0944373727195</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>7.964919124554372</v>
       </c>
       <c r="C7" t="n">
-        <v>178.9411905576576</v>
+        <v>170.0779722837174</v>
       </c>
       <c r="D7" t="n">
-        <v>34.7941203862112</v>
+        <v>33.89582123682538</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.589670517353839</v>
+        <v>4.005530633326986</v>
       </c>
       <c r="C8" t="n">
-        <v>103.9768993567797</v>
+        <v>92.21065312138165</v>
       </c>
       <c r="D8" t="n">
-        <v>32.21114217633784</v>
+        <v>31.62700229231099</v>
       </c>
     </row>
     <row r="9">
@@ -2747,7 +2747,7 @@
         <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>33.61405964570653</v>
+        <v>31.39530983410874</v>
       </c>
       <c r="D9" t="n">
         <v>32.06093477758807</v>
@@ -2764,7 +2764,7 @@
         <v>26.47773558353648</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -2772,10 +2772,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>20.7904711328347</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
         <v>23.10052348092744</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.83853571261379</v>
+        <v>15.62156946997525</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61179305066178</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
         <v>16.1301147807751</v>
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>9.919578803709772</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>30.22212132753381</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>6.138868394655306</v>
       </c>
     </row>
     <row r="18">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.399792299806704</v>
+        <v>3.401755795215198</v>
       </c>
       <c r="C2" t="n">
-        <v>6.76522342996477</v>
+        <v>7.87656183117216</v>
       </c>
       <c r="D2" t="n">
-        <v>12.16090881250524</v>
+        <v>13.83478864824605</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.98914402199105</v>
+        <v>11.44226949299657</v>
       </c>
       <c r="C3" t="n">
-        <v>17.92671307954676</v>
+        <v>15.21708941582556</v>
       </c>
       <c r="D3" t="n">
-        <v>57.62368150076654</v>
+        <v>57.8347572571796</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.15825097349554</v>
+        <v>34.30619177720055</v>
       </c>
       <c r="C4" t="n">
-        <v>78.69493247701583</v>
+        <v>84.73169911042947</v>
       </c>
       <c r="D4" t="n">
-        <v>125.7893698497353</v>
+        <v>123.4537920613322</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.75760009917161</v>
+        <v>47.66385104118265</v>
       </c>
       <c r="C5" t="n">
-        <v>171.0449937724006</v>
+        <v>222.2676802414779</v>
       </c>
       <c r="D5" t="n">
-        <v>116.0671223345792</v>
+        <v>108.1640533153924</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.49066253460771</v>
+        <v>40.85543071223103</v>
       </c>
       <c r="C6" t="n">
-        <v>234.9086636813599</v>
+        <v>300.6798693796707</v>
       </c>
       <c r="D6" t="n">
-        <v>64.08063615159783</v>
+        <v>60.25672884355649</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.48122060599696</v>
+        <v>17.42700349808513</v>
       </c>
       <c r="C7" t="n">
-        <v>230.9826546120768</v>
+        <v>246.4333999815131</v>
       </c>
       <c r="D7" t="n">
-        <v>39.1059563032632</v>
+        <v>38.44720359371359</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.258641614573416</v>
+        <v>5.340707511102648</v>
       </c>
       <c r="C8" t="n">
-        <v>160.0543282233575</v>
+        <v>146.4522137810179</v>
       </c>
       <c r="D8" t="n">
-        <v>34.04701038327938</v>
+        <v>33.29597338953057</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>69.33593161243097</v>
+        <v>61.79218225299847</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>32.17187226816798</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>25.0542014123786</v>
+        <v>24.76949457814703</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>24.52209415667683</v>
+        <v>23.63361248433346</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.22516438163779</v>
+        <v>18.00819813899924</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -3156,10 +3156,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>9.092947236733956</v>
       </c>
     </row>
     <row r="17">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.47210713921825</v>
+        <v>34.94432778496098</v>
       </c>
       <c r="D17" t="n">
         <v>4.722206457427158</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.439643045053324</v>
+        <v>2.200096605217102</v>
       </c>
       <c r="C2" t="n">
-        <v>3.410591524553419</v>
+        <v>4.445353604829558</v>
       </c>
       <c r="D2" t="n">
-        <v>9.648616437337651</v>
+        <v>10.36627400914207</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.87838645786041</v>
+        <v>11.58462291011236</v>
       </c>
       <c r="C3" t="n">
-        <v>22.25622045527519</v>
+        <v>22.64891953697392</v>
       </c>
       <c r="D3" t="n">
-        <v>54.86987919035423</v>
+        <v>56.04797643545041</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.60195987808609</v>
+        <v>30.10725684613693</v>
       </c>
       <c r="C4" t="n">
-        <v>65.31960175435728</v>
+        <v>66.37890752723959</v>
       </c>
       <c r="D4" t="n">
-        <v>126.4019804171853</v>
+        <v>124.5003351140593</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>64.45173678380311</v>
+        <v>51.22268646907735</v>
       </c>
       <c r="C5" t="n">
-        <v>166.6762164885023</v>
+        <v>204.5225904872168</v>
       </c>
       <c r="D5" t="n">
-        <v>129.2470852640926</v>
+        <v>121.8348900970292</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.8692983532775</v>
+        <v>47.97997380195012</v>
       </c>
       <c r="C6" t="n">
-        <v>259.2206638293279</v>
+        <v>332.9616973907143</v>
       </c>
       <c r="D6" t="n">
-        <v>75.47185476397357</v>
+        <v>70.80266268257573</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.28348840681585</v>
+        <v>15.75017841923158</v>
       </c>
       <c r="C7" t="n">
-        <v>276.9156844506723</v>
+        <v>312.4284441563922</v>
       </c>
       <c r="D7" t="n">
-        <v>43.59745205019235</v>
+        <v>43.23813239043802</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.090361846519712</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>203.0303339767616</v>
+        <v>192.4323675094173</v>
       </c>
       <c r="D8" t="n">
-        <v>35.88287859022092</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>82.87030546317747</v>
+        <v>72.22030636750809</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>31.8871654339364</v>
       </c>
       <c r="D10" t="n">
-        <v>25.48126166372597</v>
+        <v>25.33890824661018</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
+        <v>23.63361248433346</v>
+      </c>
+      <c r="D11" t="n">
         <v>24.34439782220815</v>
-      </c>
-      <c r="D11" t="n">
-        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>17.14033316844506</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3453,10 +3453,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>7.525096153051802</v>
       </c>
     </row>
     <row r="16">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>3.719842051391165</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.541564879845745</v>
+        <v>3.090541772968959</v>
       </c>
       <c r="C2" t="n">
-        <v>13.27322896141688</v>
+        <v>9.284388039062087</v>
       </c>
       <c r="D2" t="n">
-        <v>13.57168026350791</v>
+        <v>12.41321797249667</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.69261515757951</v>
+        <v>9.572040116406402</v>
       </c>
       <c r="C3" t="n">
-        <v>18.02488784997144</v>
+        <v>20.17491532227195</v>
       </c>
       <c r="D3" t="n">
-        <v>50.94779711188823</v>
+        <v>51.9540885087412</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.14402347955058</v>
+        <v>26.41883072128167</v>
       </c>
       <c r="C4" t="n">
-        <v>60.73778521863742</v>
+        <v>61.82261643183014</v>
       </c>
       <c r="D4" t="n">
-        <v>123.6835210241259</v>
+        <v>123.7600973450572</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>64.20629985774141</v>
+        <v>48.91557936409734</v>
       </c>
       <c r="C5" t="n">
-        <v>146.2558642401686</v>
+        <v>169.2533042121501</v>
       </c>
       <c r="D5" t="n">
-        <v>141.6907374154209</v>
+        <v>133.9349305518711</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>67.90454345963914</v>
+        <v>55.94980166502573</v>
       </c>
       <c r="C6" t="n">
-        <v>262.5212996110056</v>
+        <v>331.0698695646307</v>
       </c>
       <c r="D6" t="n">
-        <v>92.82031844571895</v>
+        <v>85.97753694711868</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.45287309576081</v>
+        <v>29.34443887993716</v>
       </c>
       <c r="C7" t="n">
-        <v>318.3572185423387</v>
+        <v>380.3997464599201</v>
       </c>
       <c r="D7" t="n">
-        <v>51.86180422454201</v>
+        <v>49.64599965605695</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.09727513817844</v>
+        <v>8.17795837637593</v>
       </c>
       <c r="C8" t="n">
-        <v>271.2078032981814</v>
+        <v>279.8864530037231</v>
       </c>
       <c r="D8" t="n">
-        <v>38.38633523605029</v>
+        <v>37.30150402285756</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.662499773917349</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>145.8828001125547</v>
+        <v>132.2374887712283</v>
       </c>
       <c r="D9" t="n">
-        <v>34.05780960802609</v>
+        <v>33.50312215512664</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>55.66018609227292</v>
+        <v>49.96604940764142</v>
       </c>
       <c r="D10" t="n">
-        <v>27.04714925199963</v>
+        <v>26.47773558353648</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>28.07602084605028</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>24.87748682561417</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>20.82875929330033</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>20.61179305066178</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
         <v>16.65044106402591</v>
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>7.166758241001715</v>
       </c>
     </row>
     <row r="16">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.151631114810514</v>
+        <v>3.965278977452867</v>
       </c>
       <c r="C2" t="n">
-        <v>5.976880023454582</v>
+        <v>4.363868545377072</v>
       </c>
       <c r="D2" t="n">
-        <v>10.18955942237764</v>
+        <v>5.464407721837746</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.212278488295564</v>
+        <v>2.208932334555323</v>
       </c>
       <c r="C2" t="n">
-        <v>7.433793616556848</v>
+        <v>5.347579745032376</v>
       </c>
       <c r="D2" t="n">
-        <v>9.988301143007048</v>
+        <v>9.135162388016569</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.52281386247382</v>
+        <v>12.80199006337841</v>
       </c>
       <c r="C3" t="n">
-        <v>31.1508546557513</v>
+        <v>27.82763867687584</v>
       </c>
       <c r="D3" t="n">
-        <v>56.44558425567036</v>
+        <v>57.04445035526092</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49.00884539600077</v>
+        <v>36.74387132684537</v>
       </c>
       <c r="C4" t="n">
-        <v>86.33980184998573</v>
+        <v>92.2617040020025</v>
       </c>
       <c r="D4" t="n">
-        <v>127.3974725892916</v>
+        <v>127.2060317869635</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.61981126321179</v>
+        <v>32.86400439966199</v>
       </c>
       <c r="C5" t="n">
-        <v>220.7950586851077</v>
+        <v>267.109006632951</v>
       </c>
       <c r="D5" t="n">
-        <v>131.0878622095554</v>
+        <v>122.1048707156971</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.01765576314322</v>
+        <v>18.19374845510189</v>
       </c>
       <c r="C6" t="n">
-        <v>263.6885976313551</v>
+        <v>315.4522270854724</v>
       </c>
       <c r="D6" t="n">
-        <v>75.19009317285472</v>
+        <v>70.56115274733101</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.647413705455153</v>
+        <v>5.389794896314989</v>
       </c>
       <c r="C7" t="n">
-        <v>190.7388527195915</v>
+        <v>196.7874003254561</v>
       </c>
       <c r="D7" t="n">
-        <v>33.59638818703009</v>
+        <v>32.5184292077671</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.835868206941535</v>
+        <v>1.752419652080557</v>
       </c>
       <c r="C8" t="n">
-        <v>107.4817386609408</v>
+        <v>97.46791207762332</v>
       </c>
       <c r="D8" t="n">
-        <v>25.03456645829366</v>
+        <v>24.61732368398877</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>42.48905889209769</v>
+        <v>38.05155926890212</v>
       </c>
       <c r="D9" t="n">
-        <v>20.63437324785945</v>
+        <v>20.1906232855399</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>22.776546738526</v>
+        <v>21.92242623583128</v>
       </c>
       <c r="D10" t="n">
-        <v>19.07535789351553</v>
+        <v>19.50241814486289</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.70345544005523</v>
+        <v>16.17036643664921</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>16.52575910558656</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.0652783745658</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="D12" t="n">
         <v>13.4519070435898</v>
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>5.838453597155781</v>
       </c>
     </row>
     <row r="15">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.770132168486005</v>
+        <v>5.957245069369645</v>
       </c>
       <c r="C2" t="n">
-        <v>8.217228284545802</v>
+        <v>7.173630474931444</v>
       </c>
       <c r="D2" t="n">
-        <v>13.01208407208722</v>
+        <v>11.09571255339745</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.06706194352505</v>
+        <v>8.433212779480101</v>
       </c>
       <c r="C3" t="n">
-        <v>15.06000978314607</v>
+        <v>11.16738013580747</v>
       </c>
       <c r="D3" t="n">
-        <v>11.69752389610075</v>
+        <v>7.942338927356696</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4557,7 +4557,7 @@
         <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4666,10 +4666,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>24.19517217116264</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.3981705161729</v>
+        <v>13.39963712548265</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14336329055224</v>
+        <v>70.15104142164446</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576255354843871</v>
+        <v>1.576427897115606</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.4168829214064</v>
+        <v>3.605959317698535</v>
       </c>
       <c r="C2" t="n">
-        <v>8.598146393793566</v>
+        <v>6.790748870275187</v>
       </c>
       <c r="D2" t="n">
-        <v>17.63807925449819</v>
+        <v>13.46368801604076</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.26188995732242</v>
+        <v>15.90922154731956</v>
       </c>
       <c r="C3" t="n">
-        <v>25.68742868161779</v>
+        <v>21.86352137357647</v>
       </c>
       <c r="D3" t="n">
-        <v>19.79694245613693</v>
+        <v>15.33980787885641</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>15.18763698469816</v>
+        <v>9.954921721062657</v>
       </c>
       <c r="C4" t="n">
-        <v>23.49616780573891</v>
+        <v>17.82952005682632</v>
       </c>
       <c r="D4" t="n">
-        <v>21.19887817780138</v>
+        <v>19.23341927389927</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.424156065963628</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
         <v>29.10881943091793</v>
@@ -4879,10 +4879,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>7.366053024963819</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
         <v>34.77743067523902</v>
@@ -4893,7 +4893,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.641744203407924</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
@@ -4910,7 +4910,7 @@
         <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>25.36836067773758</v>
       </c>
       <c r="D8" t="n">
         <v>36.80081269369168</v>
@@ -4924,7 +4924,7 @@
         <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>25.84843530511426</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4938,7 +4938,7 @@
         <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>44.22773407631881</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>4.302018440009523</v>
       </c>
       <c r="C14" t="n">
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5008,7 +5008,7 @@
         <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>26.87534340375643</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5022,7 +5022,7 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>40.5049467818149</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44149869328681</v>
+        <v>15.44628047093279</v>
       </c>
       <c r="C21" t="n">
-        <v>86.14730849938958</v>
+        <v>86.17398578520402</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250841830165644</v>
+        <v>3.251848520196378</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.147303213366026</v>
+        <v>5.026548245743669</v>
       </c>
       <c r="C2" t="n">
-        <v>4.710425484976196</v>
+        <v>7.466191290796993</v>
       </c>
       <c r="D2" t="n">
-        <v>17.53401399784803</v>
+        <v>22.38679289994002</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.02350519163969</v>
+        <v>13.98499604699582</v>
       </c>
       <c r="C3" t="n">
-        <v>30.39981766200248</v>
+        <v>24.90203051822035</v>
       </c>
       <c r="D3" t="n">
-        <v>29.31007771028852</v>
+        <v>22.55074476654924</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.75891633757857</v>
+        <v>22.02845498788993</v>
       </c>
       <c r="C4" t="n">
-        <v>47.51560713784138</v>
+        <v>39.38575439897354</v>
       </c>
       <c r="D4" t="n">
-        <v>26.35501712050563</v>
+        <v>22.4240993127014</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>13.2045066221196</v>
+        <v>9.35114688295087</v>
       </c>
       <c r="C5" t="n">
-        <v>27.04714925199963</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D5" t="n">
-        <v>30.06602344255857</v>
+        <v>29.72241174607219</v>
       </c>
     </row>
     <row r="6">
@@ -5190,10 +5190,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>5.876741757621407</v>
       </c>
       <c r="C6" t="n">
-        <v>12.11574841810989</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="D6" t="n">
         <v>36.6290068454485</v>
@@ -5204,7 +5204,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
@@ -5221,7 +5221,7 @@
         <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.54078842078653</v>
       </c>
       <c r="D8" t="n">
         <v>38.55323234577224</v>
@@ -5232,7 +5232,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
         <v>29.7312474754104</v>
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5263,7 +5263,7 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.67707142522758</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>45.77987719673301</v>
       </c>
     </row>
     <row r="13">
@@ -5288,7 +5288,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>5.203262832508096</v>
       </c>
       <c r="C13" t="n">
         <v>30.17892442854696</v>
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>4.302018440009523</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5319,10 +5319,10 @@
         <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>27.95035713990669</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.35888735806038</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5361,10 +5361,10 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>32.1031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73498751016044</v>
+        <v>16.74631463264262</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0834238119787</v>
+        <v>102.15251925912</v>
       </c>
       <c r="D21" t="n">
-        <v>5.020496253048133</v>
+        <v>5.023894389792786</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.200317589395354</v>
+        <v>5.659775514982861</v>
       </c>
       <c r="C2" t="n">
-        <v>6.997897635871265</v>
+        <v>5.782493978013713</v>
       </c>
       <c r="D2" t="n">
-        <v>14.59269787592459</v>
+        <v>20.89060939866788</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.36220814960484</v>
+        <v>15.76195939168254</v>
       </c>
       <c r="C3" t="n">
-        <v>23.39013905368026</v>
+        <v>27.3024036551038</v>
       </c>
       <c r="D3" t="n">
-        <v>36.11358930071892</v>
+        <v>34.54770171244526</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.71986741358695</v>
+        <v>24.68310078017331</v>
       </c>
       <c r="C4" t="n">
-        <v>63.46900733185205</v>
+        <v>52.44201711775187</v>
       </c>
       <c r="D4" t="n">
-        <v>34.63802250123597</v>
+        <v>28.12903522207961</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.29258617806133</v>
+        <v>21.42664364518664</v>
       </c>
       <c r="C5" t="n">
-        <v>59.56754195517523</v>
+        <v>49.60280275707011</v>
       </c>
       <c r="D5" t="n">
-        <v>32.42221793275092</v>
+        <v>31.24412068765475</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.99499345048753</v>
+        <v>9.298132506921544</v>
       </c>
       <c r="C6" t="n">
-        <v>28.37741739125406</v>
+        <v>23.54721868635975</v>
       </c>
       <c r="D6" t="n">
-        <v>38.27932473628739</v>
+        <v>38.19882142453915</v>
       </c>
     </row>
     <row r="7">
@@ -5515,7 +5515,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
         <v>21.19985992550562</v>
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.54355373745002</v>
+        <v>31.71045084717197</v>
       </c>
       <c r="D8" t="n">
         <v>40.38910055271378</v>
@@ -5543,10 +5543,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.87187407682917</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>33.83593462686631</v>
       </c>
       <c r="D9" t="n">
         <v>41.93437143919824</v>
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>33.73775985644164</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5574,10 +5574,10 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>50.46575898910303</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.06370009425158</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>47.29864089520282</v>
       </c>
     </row>
     <row r="13">
@@ -5599,7 +5599,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
         <v>33.30088212805181</v>
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>4.302018440009523</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>44.07556318216055</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5658,7 +5658,7 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
         <v>37.30543101367455</v>
@@ -5672,10 +5672,10 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>32.63820242768521</v>
       </c>
     </row>
     <row r="19">
@@ -5689,7 +5689,7 @@
         <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>25.27607639353838</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>39.67733346713483</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06091733259217</v>
+        <v>18.07991502556003</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8259845031013</v>
+        <v>117.9499218334154</v>
       </c>
       <c r="D21" t="n">
-        <v>6.88034946003511</v>
+        <v>6.887586676403819</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.685300955293279</v>
+        <v>6.532549224058276</v>
       </c>
       <c r="C2" t="n">
-        <v>5.345616249623882</v>
+        <v>8.827875356587318</v>
       </c>
       <c r="D2" t="n">
-        <v>16.6062624173348</v>
+        <v>22.34163250554466</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.67851083682156</v>
+        <v>15.96321767105314</v>
       </c>
       <c r="C3" t="n">
-        <v>24.01354884587698</v>
+        <v>23.03180114163017</v>
       </c>
       <c r="D3" t="n">
-        <v>36.85480881742526</v>
+        <v>40.20747722742812</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.39406604449724</v>
+        <v>20.50969128942011</v>
       </c>
       <c r="C4" t="n">
-        <v>50.31064285183204</v>
+        <v>51.53586398673207</v>
       </c>
       <c r="D4" t="n">
-        <v>38.70933023074748</v>
+        <v>33.38727592602553</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.70291566070749</v>
+        <v>17.96598298771663</v>
       </c>
       <c r="C5" t="n">
-        <v>67.74059159302993</v>
+        <v>55.76326960121884</v>
       </c>
       <c r="D5" t="n">
-        <v>29.99239236474006</v>
+        <v>27.93072218582176</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.28304643845935</v>
+        <v>10.54593383901924</v>
       </c>
       <c r="C6" t="n">
-        <v>42.62650357069227</v>
+        <v>35.86422538384024</v>
       </c>
       <c r="D6" t="n">
-        <v>31.03402667894593</v>
+        <v>30.47050349670826</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.689227946110266</v>
+        <v>5.030475236560656</v>
       </c>
       <c r="C7" t="n">
-        <v>20.00212772632452</v>
+        <v>17.96598298771663</v>
       </c>
       <c r="D7" t="n">
-        <v>30.72183090899544</v>
+        <v>31.14103717870882</v>
       </c>
     </row>
     <row r="8">
@@ -5843,7 +5843,7 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>18.52557917913731</v>
       </c>
       <c r="D8" t="n">
         <v>30.37527396939631</v>
@@ -5854,10 +5854,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>4.992187076095029</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>22.07656062539802</v>
       </c>
       <c r="D9" t="n">
         <v>29.95312245657017</v>
@@ -5871,7 +5871,7 @@
         <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.6377194015997</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
         <v>33.73775985644164</v>
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.61277479836603</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>34.29539255245382</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>32.32797015314322</v>
       </c>
     </row>
     <row r="13">
@@ -5910,10 +5910,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.081305133003238</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
         <v>30.17892442854696</v>
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.8226478228966</v>
       </c>
       <c r="D14" t="n">
         <v>29.80684204863741</v>
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>23.61103228713579</v>
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
         <v>17.65673246087889</v>
@@ -6000,7 +6000,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.059263391868861</v>
+        <v>7.06956019621721</v>
       </c>
       <c r="C21" t="n">
-        <v>66.18059429877057</v>
+        <v>67.16082186406349</v>
       </c>
       <c r="D21" t="n">
-        <v>5.294447543901646</v>
+        <v>5.302170147162907</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.587126184868598</v>
+        <v>4.508185457901353</v>
       </c>
       <c r="C2" t="n">
-        <v>5.421210822850886</v>
+        <v>10.46935751808799</v>
       </c>
       <c r="D2" t="n">
-        <v>23.71313404837746</v>
+        <v>18.96736564604838</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.32922963828795</v>
+        <v>20.36635612460008</v>
       </c>
       <c r="C3" t="n">
-        <v>21.98133109808609</v>
+        <v>30.55689729468197</v>
       </c>
       <c r="D3" t="n">
-        <v>42.21024254409161</v>
+        <v>49.76479112827082</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.16732338254523</v>
+        <v>27.47813649416398</v>
       </c>
       <c r="C4" t="n">
-        <v>56.70476564959152</v>
+        <v>55.58164627593317</v>
       </c>
       <c r="D4" t="n">
-        <v>49.58316780298516</v>
+        <v>47.38797993628929</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.01693605734623</v>
+        <v>25.77087723647878</v>
       </c>
       <c r="C5" t="n">
-        <v>83.59581701661591</v>
+        <v>79.86517574047804</v>
       </c>
       <c r="D5" t="n">
-        <v>38.01817984695774</v>
+        <v>34.38571334124454</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.54721868635975</v>
+        <v>18.55601335796896</v>
       </c>
       <c r="C6" t="n">
-        <v>81.50960314509145</v>
+        <v>67.94479511551327</v>
       </c>
       <c r="D6" t="n">
-        <v>33.77113927838603</v>
+        <v>32.6440929139107</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.49822911213864</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
-        <v>44.6155244194963</v>
+        <v>38.38731698375453</v>
       </c>
       <c r="D7" t="n">
-        <v>33.41672835715293</v>
+        <v>33.59638818703009</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.841398840268521</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C8" t="n">
-        <v>23.61594102565702</v>
+        <v>22.1138670381594</v>
       </c>
       <c r="D8" t="n">
-        <v>32.3780392860598</v>
+        <v>32.46148784092078</v>
       </c>
     </row>
     <row r="9">
@@ -6182,7 +6182,7 @@
         <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>24.91184799526281</v>
       </c>
       <c r="D10" t="n">
         <v>34.16482010778901</v>
@@ -6199,7 +6199,7 @@
         <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>34.82848155585983</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>22.34752299177014</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.41280136633594</v>
       </c>
     </row>
     <row r="13">
@@ -6221,7 +6221,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
         <v>21.07321447165778</v>
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
         <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -6255,7 +6255,7 @@
         <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.283440484470058</v>
+        <v>7.296130138567888</v>
       </c>
       <c r="C21" t="n">
-        <v>75.56569502637686</v>
+        <v>77.5213827222838</v>
       </c>
       <c r="D21" t="n">
-        <v>6.373010423911301</v>
+        <v>6.384113871246902</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.987679248201297</v>
+        <v>3.220132469929538</v>
       </c>
       <c r="C2" t="n">
-        <v>4.046764036905352</v>
+        <v>11.88896469842888</v>
       </c>
       <c r="D2" t="n">
-        <v>26.81742028920587</v>
+        <v>23.81719930502762</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.13426275577033</v>
+        <v>17.69109363052752</v>
       </c>
       <c r="C3" t="n">
-        <v>21.44136986075034</v>
+        <v>36.8597175559465</v>
       </c>
       <c r="D3" t="n">
-        <v>51.38467484027806</v>
+        <v>53.39234889546279</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.36625831360885</v>
+        <v>34.72736154232243</v>
       </c>
       <c r="C4" t="n">
-        <v>55.22429011158733</v>
+        <v>68.16568834896879</v>
       </c>
       <c r="D4" t="n">
-        <v>59.14244519923635</v>
+        <v>61.23553130469055</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.11006322052944</v>
+        <v>34.21390749300135</v>
       </c>
       <c r="C5" t="n">
-        <v>96.01492547533807</v>
+        <v>93.24148821084083</v>
       </c>
       <c r="D5" t="n">
-        <v>47.86020058203201</v>
+        <v>44.22773407631881</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.88560284915541</v>
+        <v>27.77364255314227</v>
       </c>
       <c r="C6" t="n">
-        <v>110.4102920627091</v>
+        <v>100.3473780941792</v>
       </c>
       <c r="D6" t="n">
-        <v>38.48058301565798</v>
+        <v>36.50825187782615</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.60099382591507</v>
+        <v>16.34904451882213</v>
       </c>
       <c r="C7" t="n">
-        <v>85.15875936177682</v>
+        <v>72.16336500066178</v>
       </c>
       <c r="D7" t="n">
-        <v>35.69241953559704</v>
+        <v>35.51275970571987</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.429686699290613</v>
+        <v>8.261406931236909</v>
       </c>
       <c r="C8" t="n">
-        <v>42.97600575340412</v>
+        <v>38.38633523605029</v>
       </c>
       <c r="D8" t="n">
-        <v>34.54770171244525</v>
+        <v>34.63115026730623</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>27.29062268265283</v>
+        <v>26.29218526743382</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -6510,7 +6510,7 @@
         <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>25.16808414607123</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.06370009425158</v>
       </c>
     </row>
     <row r="13">
@@ -6532,10 +6532,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>23.41468274628643</v>
       </c>
       <c r="D13" t="n">
         <v>31.73990327829938</v>
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
         <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>19.50241814486288</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.495211126501036</v>
+        <v>7.510409514005654</v>
       </c>
       <c r="C21" t="n">
-        <v>85.25802656394929</v>
+        <v>87.30851060031573</v>
       </c>
       <c r="D21" t="n">
-        <v>7.495211126501036</v>
+        <v>7.510409514005654</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_95_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_95_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497649924665</v>
+        <v>10.84497628215671</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907252392726</v>
+        <v>37.78907176748231</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.950552761889165</v>
+        <v>0.5998478472948011</v>
       </c>
       <c r="C2" t="n">
-        <v>8.251589454194441</v>
+        <v>2.77638250760998</v>
       </c>
       <c r="D2" t="n">
-        <v>22.39366513386975</v>
+        <v>16.70345544005523</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.06353586333556</v>
+        <v>6.337181430913161</v>
       </c>
       <c r="C3" t="n">
-        <v>42.07770660401829</v>
+        <v>32.43203540979338</v>
       </c>
       <c r="D3" t="n">
-        <v>59.61662934038756</v>
+        <v>68.86960145291374</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.29342905704534</v>
+        <v>12.69890655443249</v>
       </c>
       <c r="C4" t="n">
-        <v>80.69867954138357</v>
+        <v>95.03121427568276</v>
       </c>
       <c r="D4" t="n">
-        <v>73.51326809400116</v>
+        <v>75.14689627386785</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.61414176116455</v>
+        <v>10.57833151325938</v>
       </c>
       <c r="C5" t="n">
-        <v>110.9129468872834</v>
+        <v>140.6844460185679</v>
       </c>
       <c r="D5" t="n">
-        <v>55.14967728606459</v>
+        <v>46.80482179996669</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.15227837181205</v>
+        <v>7.003788122096746</v>
       </c>
       <c r="C6" t="n">
-        <v>125.5046630155038</v>
+        <v>115.2807424234775</v>
       </c>
       <c r="D6" t="n">
-        <v>42.22398701195107</v>
+        <v>29.90698031447059</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.09248957284423</v>
+        <v>5.449681506274044</v>
       </c>
       <c r="C7" t="n">
-        <v>109.1732899553581</v>
+        <v>62.04252791758142</v>
       </c>
       <c r="D7" t="n">
-        <v>38.26754376383641</v>
+        <v>29.10489244010094</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.01797455831271</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>68.17746932141974</v>
+        <v>31.71045084717197</v>
       </c>
       <c r="D8" t="n">
-        <v>36.21667280966483</v>
+        <v>30.95941385342316</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.09999939711293</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>37.60780930658255</v>
+        <v>30.95155987178918</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>35.16718451382499</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>3.4164820107789</v>
       </c>
       <c r="C10" t="n">
-        <v>29.75186417719959</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>37.5813021185679</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>37.49392657288993</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.98864530037232</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.75615102091507</v>
+        <v>19.77239876353076</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>27.04125876577415</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.69215749368978</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
+        <v>24.55547357862122</v>
+      </c>
+      <c r="D17" t="n">
         <v>17.9443845382232</v>
-      </c>
-      <c r="D17" t="n">
-        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>26.21757244191107</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>11.77115497391926</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>84.25358797846125</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.709819374689451</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>96.37274218361814</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.673546796525633</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.539020547360504</v>
+        <v>0.667588438887831</v>
       </c>
       <c r="C2" t="n">
-        <v>8.595201150680824</v>
+        <v>6.364670366632072</v>
       </c>
       <c r="D2" t="n">
-        <v>21.37657451227005</v>
+        <v>22.01372877232623</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.58247948825462</v>
+        <v>4.0938879267092</v>
       </c>
       <c r="C3" t="n">
-        <v>36.62409810692726</v>
+        <v>20.02765316663493</v>
       </c>
       <c r="D3" t="n">
-        <v>62.72876956284995</v>
+        <v>66.24342634405353</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.31146036862027</v>
+        <v>12.48194031179395</v>
       </c>
       <c r="C4" t="n">
-        <v>93.06575537178064</v>
+        <v>88.20315899264618</v>
       </c>
       <c r="D4" t="n">
-        <v>83.86383413987529</v>
+        <v>91.81500879657021</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.61476365597031</v>
+        <v>14.89802141194535</v>
       </c>
       <c r="C5" t="n">
-        <v>128.3635123302705</v>
+        <v>159.141302858408</v>
       </c>
       <c r="D5" t="n">
-        <v>67.54424205218056</v>
+        <v>62.24280444924779</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.05418571684538</v>
+        <v>10.38492721552276</v>
       </c>
       <c r="C6" t="n">
-        <v>150.219179722213</v>
+        <v>171.6733123031185</v>
       </c>
       <c r="D6" t="n">
-        <v>48.62400029593603</v>
+        <v>37.11202671593793</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.95570784678443</v>
+        <v>6.886960145291375</v>
       </c>
       <c r="C7" t="n">
-        <v>143.0092245822244</v>
+        <v>114.0839919720006</v>
       </c>
       <c r="D7" t="n">
-        <v>41.68108053150257</v>
+        <v>31.50035683846316</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.61041039233004</v>
+        <v>6.342090169434394</v>
       </c>
       <c r="C8" t="n">
-        <v>105.1451791248334</v>
+        <v>56.07742886657781</v>
       </c>
       <c r="D8" t="n">
-        <v>37.96909246174539</v>
+        <v>31.87734795689393</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>59.46249495082079</v>
+        <v>36.0546844384641</v>
       </c>
       <c r="D9" t="n">
-        <v>35.94374694788421</v>
+        <v>35.49999698556465</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.121196935978863</v>
+        <v>4.128249096357838</v>
       </c>
       <c r="C10" t="n">
-        <v>37.29659528433633</v>
+        <v>34.02246669067321</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>38.43542262126263</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>32.69612554223576</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>38.38240824523329</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.8092064546734</v>
+        <v>28.63954402828795</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>38.18605870438393</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>28.35778243716912</v>
+        <v>22.37403017978481</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>36.94316611080748</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>28.5776939229204</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>27.69215749368978</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>26.44435616159209</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>50.2949348885641</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>9.63094497866121</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>45.7376620454504</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.893343092237959</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>105.5734638586827</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.866678865297448</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.701409829188727</v>
+        <v>0.3573561643458389</v>
       </c>
       <c r="C2" t="n">
-        <v>9.951976477949916</v>
+        <v>2.709623663721197</v>
       </c>
       <c r="D2" t="n">
-        <v>19.69091370407828</v>
+        <v>15.00110492089126</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.59015354343935</v>
+        <v>3.740458753180347</v>
       </c>
       <c r="C3" t="n">
-        <v>34.7980473770282</v>
+        <v>23.49813130114741</v>
       </c>
       <c r="D3" t="n">
-        <v>64.26520471999621</v>
+        <v>69.80226177194821</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.69510273680252</v>
+        <v>13.40085616296896</v>
       </c>
       <c r="C4" t="n">
-        <v>91.17687278880977</v>
+        <v>81.79627347473149</v>
       </c>
       <c r="D4" t="n">
-        <v>93.47416241674732</v>
+        <v>101.9230831594954</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.51029748869265</v>
+        <v>14.60349710067131</v>
       </c>
       <c r="C5" t="n">
-        <v>147.5566799482956</v>
+        <v>182.4823545268759</v>
       </c>
       <c r="D5" t="n">
-        <v>78.3189231062893</v>
+        <v>70.21950454625312</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.21898046243861</v>
+        <v>8.855364292306232</v>
       </c>
       <c r="C6" t="n">
-        <v>172.2770871412303</v>
+        <v>212.6494979829719</v>
       </c>
       <c r="D6" t="n">
-        <v>56.91584140600459</v>
+        <v>37.83655652167208</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>43.29801900039708</v>
+        <v>4.19206269713388</v>
       </c>
       <c r="C7" t="n">
-        <v>174.6293546406056</v>
+        <v>106.1190728474462</v>
       </c>
       <c r="D7" t="n">
-        <v>45.03473068920969</v>
+        <v>33.17718191731671</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>27.12078032981814</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>142.8639259219958</v>
+        <v>45.72980806381643</v>
       </c>
       <c r="D8" t="n">
-        <v>40.3056519978528</v>
+        <v>36.13322425480386</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.97812381306608</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>89.52655489797087</v>
+        <v>25.95937279569415</v>
       </c>
       <c r="D9" t="n">
-        <v>37.05312185368311</v>
+        <v>40.04843409934012</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>51.67429041303087</v>
+        <v>26.1930287493049</v>
       </c>
       <c r="D10" t="n">
-        <v>36.44247478164161</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>37.13853390395258</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>30.56376952861169</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>33.41280136633594</v>
+        <v>18.22516438163779</v>
       </c>
       <c r="D12" t="n">
-        <v>36.01639627799849</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>30.95941385342317</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>20.89551813718911</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>27.69215749368978</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>43.44429940832985</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>8.02775097762617</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>39.59388491227386</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.060567289548368</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>113.8555129648707</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11.083280023129</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.032839642596649</v>
+        <v>0.6882051406770141</v>
       </c>
       <c r="C2" t="n">
-        <v>6.767186925373263</v>
+        <v>3.946625771072178</v>
       </c>
       <c r="D2" t="n">
-        <v>16.24596100987622</v>
+        <v>16.38046044535803</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.03608798534566</v>
+        <v>2.45927799913826</v>
       </c>
       <c r="C3" t="n">
-        <v>53.51506735849363</v>
+        <v>16.33628179866693</v>
       </c>
       <c r="D3" t="n">
-        <v>69.92498023497907</v>
+        <v>65.74764375340889</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.33476027161494</v>
+        <v>10.51648140789183</v>
       </c>
       <c r="C4" t="n">
-        <v>124.423758793128</v>
+        <v>70.14390997302611</v>
       </c>
       <c r="D4" t="n">
-        <v>90.06651613530664</v>
+        <v>112.5671917689393</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.53235360207581</v>
+        <v>17.32784697995621</v>
       </c>
       <c r="C5" t="n">
-        <v>102.9362467902781</v>
+        <v>168.0997506596601</v>
       </c>
       <c r="D5" t="n">
-        <v>55.0515025156399</v>
+        <v>88.60273030827464</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.88810612391165</v>
+        <v>13.44405306195583</v>
       </c>
       <c r="C6" t="n">
-        <v>114.9989808323586</v>
+        <v>254.5917234038041</v>
       </c>
       <c r="D6" t="n">
-        <v>29.62521872335175</v>
+        <v>49.54978838104078</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.96598298771663</v>
+        <v>6.587527095496098</v>
       </c>
       <c r="C7" t="n">
-        <v>100.429844901336</v>
+        <v>198.763658454105</v>
       </c>
       <c r="D7" t="n">
-        <v>28.32636651063322</v>
+        <v>36.29128563518759</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.680032363873551</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>65.92435834017331</v>
+        <v>86.61959994569608</v>
       </c>
       <c r="D8" t="n">
-        <v>27.28767743954009</v>
+        <v>37.30150402285756</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>3.328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>39.38280915586078</v>
+        <v>38.93905919354123</v>
       </c>
       <c r="D9" t="n">
-        <v>27.73437264497238</v>
+        <v>40.71405904281946</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>29.04009709162065</v>
+        <v>29.32480392585223</v>
       </c>
       <c r="D10" t="n">
-        <v>28.75539025738908</v>
+        <v>31.8871654339364</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>28.78680618392497</v>
+        <v>31.27455486648638</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
-        <v>26.90381408717959</v>
+        <v>31.02617269731195</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
+        <v>21.51009220004762</v>
+      </c>
+      <c r="D14" t="n">
         <v>20.58823110575986</v>
-      </c>
-      <c r="D14" t="n">
-        <v>24.27567548291088</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>23.29196428325557</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>37.19842051391164</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>12.81278928812512</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>46.74984392852887</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>5.194427103169874</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.628981483252716</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.68744437715102</v>
+        <v>0.4624031687002477</v>
       </c>
       <c r="C2" t="n">
-        <v>3.262347621212151</v>
+        <v>3.520547267429062</v>
       </c>
       <c r="D2" t="n">
-        <v>12.10004045484194</v>
+        <v>11.43147026824986</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.43507846389736</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C3" t="n">
-        <v>40.2761995667254</v>
+        <v>16.2037458585936</v>
       </c>
       <c r="D3" t="n">
-        <v>67.43134106619218</v>
+        <v>64.78553100324702</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.02242563294421</v>
+        <v>8.474446183058468</v>
       </c>
       <c r="C4" t="n">
-        <v>133.5235782637917</v>
+        <v>58.21076662790613</v>
       </c>
       <c r="D4" t="n">
-        <v>103.1483042943954</v>
+        <v>118.6294838426633</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.40396563699773</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="C5" t="n">
-        <v>161.0066234964769</v>
+        <v>157.6686813020378</v>
       </c>
       <c r="D5" t="n">
-        <v>69.1641257641878</v>
+        <v>103.5498391054324</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.52333794628834</v>
+        <v>16.30192062901829</v>
       </c>
       <c r="C6" t="n">
-        <v>141.0820538387879</v>
+        <v>272.3829553001648</v>
       </c>
       <c r="D6" t="n">
-        <v>35.94472869558847</v>
+        <v>59.08943082320704</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.88802400845363</v>
+        <v>7.186393195086651</v>
       </c>
       <c r="C7" t="n">
-        <v>128.6364381920511</v>
+        <v>263.4411972098848</v>
       </c>
       <c r="D7" t="n">
-        <v>30.78171751895449</v>
+        <v>39.76470901281281</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>87.2871883845839</v>
+        <v>132.5997536740954</v>
       </c>
       <c r="D8" t="n">
-        <v>28.45595720759379</v>
+        <v>40.05530633326986</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.548437113775471</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>45.48437113775471</v>
+        <v>51.03124566674919</v>
       </c>
       <c r="D9" t="n">
-        <v>28.73281006019139</v>
+        <v>40.82499653339935</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>31.8871654339364</v>
+        <v>31.60245859970483</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>32.74128593663113</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>27.18753917370691</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>32.69612554223576</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>22.56448923440869</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.91060420565131</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>31.53373626040754</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.75013736150257</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>40.09163099832699</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>4.133157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>12.27773678931061</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>8.025787482217675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.282964323001334</v>
+        <v>0.703913103944963</v>
       </c>
       <c r="C2" t="n">
-        <v>4.265693774952391</v>
+        <v>4.93720920465721</v>
       </c>
       <c r="D2" t="n">
-        <v>16.18214740910017</v>
+        <v>16.28719441345458</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.43936530761284</v>
+        <v>2.012582793705961</v>
       </c>
       <c r="C3" t="n">
-        <v>25.34381698513141</v>
+        <v>14.97165248976386</v>
       </c>
       <c r="D3" t="n">
-        <v>62.43915399009714</v>
+        <v>59.3908273684108</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.089225534562</v>
+        <v>6.71319080163969</v>
       </c>
       <c r="C4" t="n">
-        <v>117.6467543907123</v>
+        <v>49.43001516112266</v>
       </c>
       <c r="D4" t="n">
-        <v>111.7886658394716</v>
+        <v>123.1474867776072</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.28816046562561</v>
+        <v>15.87976911619216</v>
       </c>
       <c r="C5" t="n">
-        <v>202.7063572343602</v>
+        <v>133.7385810110218</v>
       </c>
       <c r="D5" t="n">
-        <v>86.22199212547613</v>
+        <v>119.5277829920492</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.31957639216151</v>
+        <v>19.72331137831842</v>
       </c>
       <c r="C6" t="n">
-        <v>196.5488356333242</v>
+        <v>266.5062135425434</v>
       </c>
       <c r="D6" t="n">
-        <v>47.69821221083129</v>
+        <v>74.22405343187586</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.81112889235289</v>
+        <v>11.91743538185203</v>
       </c>
       <c r="C7" t="n">
-        <v>163.6102184081394</v>
+        <v>321.6509820900868</v>
       </c>
       <c r="D7" t="n">
-        <v>33.53650157707104</v>
+        <v>45.93302983859552</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.01659189998096</v>
+        <v>5.507604620824606</v>
       </c>
       <c r="C8" t="n">
-        <v>125.9238692852171</v>
+        <v>225.7283408989479</v>
       </c>
       <c r="D8" t="n">
-        <v>29.95803119509142</v>
+        <v>41.55738032076748</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>3.328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>73.21874378272709</v>
+        <v>96.84842927624356</v>
       </c>
       <c r="D9" t="n">
-        <v>29.50937249425062</v>
+        <v>42.26718391093791</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>1.70824100538945</v>
       </c>
       <c r="C10" t="n">
-        <v>41.14013754646259</v>
+        <v>43.41779222031519</v>
       </c>
       <c r="D10" t="n">
-        <v>30.7483380970101</v>
+        <v>34.30717352490479</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>33.22921454564179</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>25.81898287398687</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>24.45533531278805</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>19.66637001147211</v>
+        <v>16.90078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>32.6087499965578</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>40.09163099832699</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.956623174563893</v>
+        <v>0.4781111319681966</v>
       </c>
       <c r="C2" t="n">
-        <v>2.036144738607885</v>
+        <v>2.607521902479529</v>
       </c>
       <c r="D2" t="n">
-        <v>11.28028112179585</v>
+        <v>11.85656702418873</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.85031668506475</v>
+        <v>2.881429511964388</v>
       </c>
       <c r="C3" t="n">
-        <v>23.2232419439583</v>
+        <v>18.78574232076272</v>
       </c>
       <c r="D3" t="n">
-        <v>62.95948027334795</v>
+        <v>65.14877765381833</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.81593981988289</v>
+        <v>10.93765117301371</v>
       </c>
       <c r="C4" t="n">
-        <v>109.5934779727757</v>
+        <v>72.12213159708342</v>
       </c>
       <c r="D4" t="n">
-        <v>118.5529075217321</v>
+        <v>126.0318615326843</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.37437433715008</v>
+        <v>11.97732199181109</v>
       </c>
       <c r="C5" t="n">
-        <v>236.5766530308752</v>
+        <v>213.4564945958628</v>
       </c>
       <c r="D5" t="n">
-        <v>91.25344910974104</v>
+        <v>110.0784613386736</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.5975498611836</v>
+        <v>7.366053024963819</v>
       </c>
       <c r="C6" t="n">
-        <v>236.5992332280728</v>
+        <v>274.5162930614932</v>
       </c>
       <c r="D6" t="n">
-        <v>47.0944373727195</v>
+        <v>63.11459641061895</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.964919124554372</v>
+        <v>3.593196597543325</v>
       </c>
       <c r="C7" t="n">
-        <v>170.0779722837174</v>
+        <v>158.6995163914969</v>
       </c>
       <c r="D7" t="n">
-        <v>33.89582123682538</v>
+        <v>35.51275970571987</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.005530633326986</v>
+        <v>2.253110981246429</v>
       </c>
       <c r="C8" t="n">
-        <v>92.21065312138165</v>
+        <v>71.34851440613694</v>
       </c>
       <c r="D8" t="n">
-        <v>31.62700229231099</v>
+        <v>31.12631096314512</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>31.39530983410874</v>
+        <v>33.05937219280708</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>26.18124777685393</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>26.47773558353648</v>
+        <v>24.20008090968388</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>26.05067533218912</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.61277479836603</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.62156946997525</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>13.78864650614645</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>27.3485457972034</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>8.604036880019047</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>34.04210164475815</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>2.866703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.919578803709772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30.22212132753381</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>6.138868394655306</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30.49799243242716</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.401755795215198</v>
+        <v>0.2464186737659494</v>
       </c>
       <c r="C2" t="n">
-        <v>7.87656183117216</v>
+        <v>2.669372007847077</v>
       </c>
       <c r="D2" t="n">
-        <v>13.83478864824605</v>
+        <v>9.405143006684444</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.44226949299657</v>
+        <v>2.272745935331366</v>
       </c>
       <c r="C3" t="n">
-        <v>15.21708941582556</v>
+        <v>14.13225820263284</v>
       </c>
       <c r="D3" t="n">
-        <v>57.8347572571796</v>
+        <v>59.63135555595126</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.30619177720055</v>
+        <v>7.746971134211581</v>
       </c>
       <c r="C4" t="n">
-        <v>84.73169911042947</v>
+        <v>57.29185077673112</v>
       </c>
       <c r="D4" t="n">
-        <v>123.4537920613322</v>
+        <v>124.2706061512655</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.66385104118265</v>
+        <v>11.19192382841364</v>
       </c>
       <c r="C5" t="n">
-        <v>222.2676802414779</v>
+        <v>157.1532637573082</v>
       </c>
       <c r="D5" t="n">
-        <v>108.1640533153924</v>
+        <v>116.3616466458532</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.85543071223103</v>
+        <v>7.084291433844984</v>
       </c>
       <c r="C6" t="n">
-        <v>300.6798693796707</v>
+        <v>254.7527300273006</v>
       </c>
       <c r="D6" t="n">
-        <v>60.25672884355649</v>
+        <v>66.93850371866029</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.42700349808513</v>
+        <v>2.87455727803466</v>
       </c>
       <c r="C7" t="n">
-        <v>246.4333999815131</v>
+        <v>191.3377188191821</v>
       </c>
       <c r="D7" t="n">
-        <v>38.44720359371359</v>
+        <v>34.31502750653876</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.340707511102648</v>
+        <v>1.168279768053704</v>
       </c>
       <c r="C8" t="n">
-        <v>146.4522137810179</v>
+        <v>82.5306207575081</v>
       </c>
       <c r="D8" t="n">
-        <v>33.29597338953057</v>
+        <v>26.78698611037422</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>61.79218225299847</v>
+        <v>32.39374724932775</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>20.74531073843935</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>17.65182372235765</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>19.92947839621025</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.63361248433346</v>
+        <v>13.14952875068177</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>17.59193711239859</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.00819813899924</v>
+        <v>11.49921085984289</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>13.23494080095125</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.60978849752428</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>8.065057390387548</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.94432778496098</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.200096605217102</v>
+        <v>0.3534291735288517</v>
       </c>
       <c r="C2" t="n">
-        <v>4.445353604829558</v>
+        <v>3.496003574822891</v>
       </c>
       <c r="D2" t="n">
-        <v>10.36627400914207</v>
+        <v>9.788024611340701</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.58462291011236</v>
+        <v>1.497165248976386</v>
       </c>
       <c r="C3" t="n">
-        <v>22.64891953697392</v>
+        <v>11.88896469842887</v>
       </c>
       <c r="D3" t="n">
-        <v>56.04797643545041</v>
+        <v>53.89304022462866</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.10725684613693</v>
+        <v>5.985715752792802</v>
       </c>
       <c r="C4" t="n">
-        <v>66.37890752723959</v>
+        <v>45.20555478974863</v>
       </c>
       <c r="D4" t="n">
-        <v>124.5003351140593</v>
+        <v>124.9087421590259</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.22268646907735</v>
+        <v>11.70734137314322</v>
       </c>
       <c r="C5" t="n">
-        <v>204.5225904872168</v>
+        <v>129.0752794158494</v>
       </c>
       <c r="D5" t="n">
-        <v>121.8348900970292</v>
+        <v>135.1866588747858</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.97997380195012</v>
+        <v>11.10945702125691</v>
       </c>
       <c r="C6" t="n">
-        <v>332.9616973907143</v>
+        <v>255.9602797035242</v>
       </c>
       <c r="D6" t="n">
-        <v>70.80266268257573</v>
+        <v>87.38634490271285</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.75017841923158</v>
+        <v>5.449681506274044</v>
       </c>
       <c r="C7" t="n">
-        <v>312.4284441563922</v>
+        <v>283.2037784963731</v>
       </c>
       <c r="D7" t="n">
-        <v>43.23813239043802</v>
+        <v>44.79518424937346</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.422773407631881</v>
+        <v>2.002765316663493</v>
       </c>
       <c r="C8" t="n">
-        <v>192.4323675094173</v>
+        <v>169.817809142092</v>
       </c>
       <c r="D8" t="n">
-        <v>34.29735604786232</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>0.6656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>72.22030636750809</v>
+        <v>66.78436932909349</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>22.52031058771757</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>31.8871654339364</v>
+        <v>27.75891633757857</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>20.4988920646734</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.63361248433346</v>
+        <v>16.70345544005523</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>18.30272245027328</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>13.23494080095125</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>13.88583952886689</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>8.585383673638358</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>3.380157345721768</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="D15" t="n">
-        <v>7.525096153051802</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.090541772968959</v>
+        <v>0.2395464398362217</v>
       </c>
       <c r="C2" t="n">
-        <v>9.284388039062087</v>
+        <v>8.983973241562561</v>
       </c>
       <c r="D2" t="n">
-        <v>12.41321797249667</v>
+        <v>11.5728419376614</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.572040116406402</v>
+        <v>1.335176877775662</v>
       </c>
       <c r="C3" t="n">
-        <v>20.17491532227195</v>
+        <v>12.772537632251</v>
       </c>
       <c r="D3" t="n">
-        <v>51.9540885087412</v>
+        <v>49.47026681699678</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.41883072128167</v>
+        <v>4.415901173702153</v>
       </c>
       <c r="C4" t="n">
-        <v>61.82261643183014</v>
+        <v>36.98636300979434</v>
       </c>
       <c r="D4" t="n">
-        <v>123.7600973450572</v>
+        <v>123.7345719047467</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.91557936409734</v>
+        <v>10.4801567428347</v>
       </c>
       <c r="C5" t="n">
-        <v>169.2533042121501</v>
+        <v>105.7342277473815</v>
       </c>
       <c r="D5" t="n">
-        <v>133.9349305518711</v>
+        <v>146.9185439405352</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.94980166502573</v>
+        <v>13.52455637370406</v>
       </c>
       <c r="C6" t="n">
-        <v>331.0698695646307</v>
+        <v>229.9979616647173</v>
       </c>
       <c r="D6" t="n">
-        <v>85.97753694711868</v>
+        <v>108.1159476778843</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.34443887993716</v>
+        <v>9.102764713776425</v>
       </c>
       <c r="C7" t="n">
-        <v>380.3997464599201</v>
+        <v>328.9571485050915</v>
       </c>
       <c r="D7" t="n">
-        <v>49.64599965605695</v>
+        <v>57.67080539057038</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.17795837637593</v>
+        <v>3.75518496874405</v>
       </c>
       <c r="C8" t="n">
-        <v>279.8864530037231</v>
+        <v>271.0409061884594</v>
       </c>
       <c r="D8" t="n">
-        <v>37.30150402285756</v>
+        <v>34.13045893814036</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>132.2374887712283</v>
+        <v>135.2328010168853</v>
       </c>
       <c r="D9" t="n">
-        <v>33.50312215512664</v>
+        <v>24.84999788989526</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>49.96604940764142</v>
+        <v>51.53193699591508</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>21.35301256736813</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.07602084605028</v>
+        <v>23.63361248433346</v>
       </c>
       <c r="D11" t="n">
-        <v>24.87748682561417</v>
+        <v>19.01350778814797</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>15.83853571261379</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61179305066178</v>
+        <v>14.53673825678252</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>3.994731408580272</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>8.241771977151972</v>
       </c>
       <c r="D15" t="n">
-        <v>7.166758241001715</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.965278977452867</v>
+        <v>1.404880964777186</v>
       </c>
       <c r="C2" t="n">
-        <v>4.363868545377072</v>
+        <v>19.83032187808132</v>
       </c>
       <c r="D2" t="n">
-        <v>5.464407721837746</v>
+        <v>16.0525567121396</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.208932334555323</v>
+        <v>0.4682936549257286</v>
       </c>
       <c r="C2" t="n">
-        <v>5.347579745032376</v>
+        <v>11.2351207274005</v>
       </c>
       <c r="D2" t="n">
-        <v>9.135162388016569</v>
+        <v>14.93336432929823</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.80199006337841</v>
+        <v>1.065196259107789</v>
       </c>
       <c r="C3" t="n">
-        <v>27.82763867687584</v>
+        <v>23.62084976417826</v>
       </c>
       <c r="D3" t="n">
-        <v>57.04445035526092</v>
+        <v>47.29569565209009</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.74387132684537</v>
+        <v>3.471459882216722</v>
       </c>
       <c r="C4" t="n">
-        <v>92.2617040020025</v>
+        <v>34.11475097487241</v>
       </c>
       <c r="D4" t="n">
-        <v>127.2060317869635</v>
+        <v>119.5356369736831</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.86400439966199</v>
+        <v>8.909360416039807</v>
       </c>
       <c r="C5" t="n">
-        <v>267.109006632951</v>
+        <v>87.91550691530188</v>
       </c>
       <c r="D5" t="n">
-        <v>122.1048707156971</v>
+        <v>156.4169529791231</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.19374845510189</v>
+        <v>13.84656962069702</v>
       </c>
       <c r="C6" t="n">
-        <v>315.4522270854724</v>
+        <v>203.3513654760503</v>
       </c>
       <c r="D6" t="n">
-        <v>70.56115274733101</v>
+        <v>124.7398815538955</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.389794896314989</v>
+        <v>12.21686843164731</v>
       </c>
       <c r="C7" t="n">
-        <v>196.7874003254561</v>
+        <v>331.1729530735765</v>
       </c>
       <c r="D7" t="n">
-        <v>32.5184292077671</v>
+        <v>72.22325161062085</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.752419652080557</v>
+        <v>6.258641614573416</v>
       </c>
       <c r="C8" t="n">
-        <v>97.46791207762332</v>
+        <v>347.9804737702819</v>
       </c>
       <c r="D8" t="n">
-        <v>24.61732368398877</v>
+        <v>39.72151211382594</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>38.05155926890212</v>
+        <v>221.985918650359</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>27.40156017323271</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>21.92242623583128</v>
+        <v>98.08150439277759</v>
       </c>
       <c r="D10" t="n">
-        <v>19.50241814486289</v>
+        <v>22.34948648717864</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.17036643664921</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>16.52575910558656</v>
+        <v>19.36890045708532</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.84831213192725</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>15.4046032273367</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>15.60978849752428</v>
+      </c>
+      <c r="D13" t="n">
         <v>9.886199381765381</v>
-      </c>
-      <c r="D13" t="n">
-        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>5.838453597155781</v>
+        <v>4.609305471438775</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>11.46681318560274</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>0.7166758241001715</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.957245069369645</v>
+        <v>3.311435006424491</v>
       </c>
       <c r="C2" t="n">
-        <v>7.173630474931444</v>
+        <v>11.30973355292326</v>
       </c>
       <c r="D2" t="n">
-        <v>11.09571255339745</v>
+        <v>17.93260356577224</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.433212779480101</v>
+        <v>2.282563412373834</v>
       </c>
       <c r="C3" t="n">
-        <v>11.16738013580747</v>
+        <v>39.1520984453628</v>
       </c>
       <c r="D3" t="n">
-        <v>7.942338927356696</v>
+        <v>13.94081740030471</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.657010198319369</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>8.29576810088555</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.675483478250811</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.32958949118645</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>24.19517217116264</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39963712548265</v>
+        <v>11.67652792549844</v>
       </c>
       <c r="C21" t="n">
-        <v>70.15104142164446</v>
+        <v>59.93951001755868</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576427897115606</v>
+        <v>0.7784351950332296</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.605959317698535</v>
+        <v>3.019855938263189</v>
       </c>
       <c r="C2" t="n">
-        <v>6.790748870275187</v>
+        <v>4.558254590817941</v>
       </c>
       <c r="D2" t="n">
-        <v>13.46368801604076</v>
+        <v>15.80319279526091</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.90922154731956</v>
+        <v>8.045422436302612</v>
       </c>
       <c r="C3" t="n">
-        <v>21.86352137357647</v>
+        <v>42.48022316275949</v>
       </c>
       <c r="D3" t="n">
-        <v>15.33980787885641</v>
+        <v>26.21757244191107</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>9.954921721062657</v>
+        <v>3.101340997715674</v>
       </c>
       <c r="C4" t="n">
-        <v>17.82952005682632</v>
+        <v>63.16270204812704</v>
       </c>
       <c r="D4" t="n">
-        <v>19.23341927389927</v>
+        <v>21.64557338323367</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.129631754689585</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.366053024963819</v>
+        <v>5.474225198880216</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>13.72581465307466</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.22360179685679</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.842781498600267</v>
       </c>
       <c r="C8" t="n">
-        <v>25.36836067773758</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.84843530511426</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.72187196672443</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.8329640215578</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>44.84132639147307</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.302018440009523</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.87534340375643</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44628047093279</v>
+        <v>13.62367241844358</v>
       </c>
       <c r="C21" t="n">
-        <v>86.17398578520402</v>
+        <v>73.72810955863581</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251848520196378</v>
+        <v>1.602784990405126</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.026548245743669</v>
+        <v>1.780890335503714</v>
       </c>
       <c r="C2" t="n">
-        <v>7.466191290796993</v>
+        <v>4.283365233628834</v>
       </c>
       <c r="D2" t="n">
-        <v>22.38679289994002</v>
+        <v>20.61964703229576</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.98499604699582</v>
+        <v>9.518043992672828</v>
       </c>
       <c r="C3" t="n">
-        <v>24.90203051822035</v>
+        <v>27.20422888467912</v>
       </c>
       <c r="D3" t="n">
-        <v>22.55074476654924</v>
+        <v>33.15361997241479</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.02845498788993</v>
+        <v>10.42714236680537</v>
       </c>
       <c r="C4" t="n">
-        <v>39.38575439897354</v>
+        <v>89.53048188878786</v>
       </c>
       <c r="D4" t="n">
-        <v>22.4240993127014</v>
+        <v>30.36251124924111</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>9.35114688295087</v>
+        <v>3.657010198319369</v>
       </c>
       <c r="C5" t="n">
-        <v>21.35301256736813</v>
+        <v>70.85764055401356</v>
       </c>
       <c r="D5" t="n">
-        <v>29.72241174607219</v>
+        <v>27.9798095710341</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.876741757621407</v>
+        <v>4.508185457901354</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>10.58618549489336</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>31.55729820530948</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.82246789644735</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.42692138262712</v>
       </c>
       <c r="C8" t="n">
-        <v>29.54078842078653</v>
+        <v>23.699389580518</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>23.96249796525614</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>36.27655941962388</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.260024272905163</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.77947628610551</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.508987279156352</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>31.67707142522758</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>41.44055234396211</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.302018440009523</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.95035713990669</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74631463264262</v>
+        <v>14.82754992165041</v>
       </c>
       <c r="C21" t="n">
-        <v>102.15251925912</v>
+        <v>87.31779398305243</v>
       </c>
       <c r="D21" t="n">
-        <v>5.023894389792786</v>
+        <v>2.471258320275069</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.659775514982861</v>
+        <v>1.777945092390974</v>
       </c>
       <c r="C2" t="n">
-        <v>5.782493978013713</v>
+        <v>3.1857713002809</v>
       </c>
       <c r="D2" t="n">
-        <v>20.89060939866788</v>
+        <v>19.41406085148067</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.76195939168254</v>
+        <v>7.706719478337462</v>
       </c>
       <c r="C3" t="n">
-        <v>27.3024036551038</v>
+        <v>20.9014086234146</v>
       </c>
       <c r="D3" t="n">
-        <v>34.54770171244526</v>
+        <v>41.95498814098744</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.68310078017331</v>
+        <v>14.81751810019711</v>
       </c>
       <c r="C4" t="n">
-        <v>52.44201711775187</v>
+        <v>77.18893149870122</v>
       </c>
       <c r="D4" t="n">
-        <v>28.12903522207961</v>
+        <v>40.15151760828606</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21.42664364518664</v>
+        <v>9.866564427680446</v>
       </c>
       <c r="C5" t="n">
-        <v>49.60280275707011</v>
+        <v>123.8474728907351</v>
       </c>
       <c r="D5" t="n">
-        <v>31.24412068765475</v>
+        <v>32.66765485881262</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.298132506921544</v>
+        <v>4.789947049020189</v>
       </c>
       <c r="C6" t="n">
-        <v>23.54721868635975</v>
+        <v>65.0869275484508</v>
       </c>
       <c r="D6" t="n">
-        <v>38.19882142453915</v>
+        <v>33.2881194078966</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>17.66654993792135</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>31.71045084717197</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>35.79943003535994</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.87187407682917</v>
+        <v>7.765624340592267</v>
       </c>
       <c r="C9" t="n">
-        <v>33.83593462686631</v>
+        <v>27.5124976638126</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>36.94218436310322</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.73775985644164</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.930157044278233</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>45.31256528951153</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.06370009425158</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>47.29864089520282</v>
+        <v>42.95931604243193</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.62610266006477</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.302018440009523</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.44199175555609</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.63820242768521</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.07991502556003</v>
+        <v>16.05942467240069</v>
       </c>
       <c r="C21" t="n">
-        <v>117.9499218334154</v>
+        <v>100.582712421878</v>
       </c>
       <c r="D21" t="n">
-        <v>6.887586676403819</v>
+        <v>3.380931509979093</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.532549224058276</v>
+        <v>1.435315143608837</v>
       </c>
       <c r="C2" t="n">
-        <v>8.827875356587318</v>
+        <v>6.655267687089128</v>
       </c>
       <c r="D2" t="n">
-        <v>22.34163250554466</v>
+        <v>31.15576339427253</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.96321767105314</v>
+        <v>6.813329067472864</v>
       </c>
       <c r="C3" t="n">
-        <v>23.03180114163017</v>
+        <v>16.03684874887165</v>
       </c>
       <c r="D3" t="n">
-        <v>40.20747722742812</v>
+        <v>47.37423546842984</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.50969128942011</v>
+        <v>14.91961986143878</v>
       </c>
       <c r="C4" t="n">
-        <v>51.53586398673207</v>
+        <v>63.52005821247288</v>
       </c>
       <c r="D4" t="n">
-        <v>33.38727592602553</v>
+        <v>51.49757582626644</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>17.96598298771663</v>
+        <v>15.85522542358599</v>
       </c>
       <c r="C5" t="n">
-        <v>55.76326960121884</v>
+        <v>133.7631247036279</v>
       </c>
       <c r="D5" t="n">
-        <v>27.93072218582176</v>
+        <v>39.3680829402971</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.54593383901924</v>
+        <v>9.016370915802709</v>
       </c>
       <c r="C6" t="n">
-        <v>35.86422538384024</v>
+        <v>131.3009014613769</v>
       </c>
       <c r="D6" t="n">
-        <v>30.47050349670826</v>
+        <v>35.783722072092</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.030475236560656</v>
+        <v>6.228207435741766</v>
       </c>
       <c r="C7" t="n">
-        <v>17.96598298771663</v>
+        <v>56.41318658143022</v>
       </c>
       <c r="D7" t="n">
-        <v>31.14103717870882</v>
+        <v>37.00992495469625</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.11801501315464</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>37.05115835827462</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>30.39687241888974</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>38.162496759482</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.285549713215578</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>30.38607319414302</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>31.24313893995049</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>44.04414725562465</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.081305133003238</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>42.40659208494097</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.8226478228966</v>
+        <v>28.5776939229204</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>26.87534340375643</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.06956019621721</v>
+        <v>17.3143884331555</v>
       </c>
       <c r="C21" t="n">
-        <v>67.16082186406349</v>
+        <v>114.2749636588263</v>
       </c>
       <c r="D21" t="n">
-        <v>5.302170147162907</v>
+        <v>4.328597108288876</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.508185457901353</v>
+        <v>1.063232763699296</v>
       </c>
       <c r="C2" t="n">
-        <v>10.46935751808799</v>
+        <v>11.19094208070939</v>
       </c>
       <c r="D2" t="n">
-        <v>18.96736564604838</v>
+        <v>30.46657650589127</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.36635612460008</v>
+        <v>5.772676500971246</v>
       </c>
       <c r="C3" t="n">
-        <v>30.55689729468197</v>
+        <v>21.11739311834889</v>
       </c>
       <c r="D3" t="n">
-        <v>49.76479112827082</v>
+        <v>58.9294059474148</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.47813649416398</v>
+        <v>13.98794129010856</v>
       </c>
       <c r="C4" t="n">
-        <v>55.58164627593317</v>
+        <v>50.89772797897164</v>
       </c>
       <c r="D4" t="n">
-        <v>47.38797993628929</v>
+        <v>61.13342954344888</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.77087723647878</v>
+        <v>18.80046853632642</v>
       </c>
       <c r="C5" t="n">
-        <v>79.86517574047804</v>
+        <v>125.3937255249239</v>
       </c>
       <c r="D5" t="n">
-        <v>34.38571334124454</v>
+        <v>47.88474427463818</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.55601335796896</v>
+        <v>14.77235770580176</v>
       </c>
       <c r="C6" t="n">
-        <v>67.94479511551327</v>
+        <v>170.5462659386432</v>
       </c>
       <c r="D6" t="n">
-        <v>32.6440929139107</v>
+        <v>39.36611944488861</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>8.324238784308704</v>
       </c>
       <c r="C7" t="n">
-        <v>38.38731698375453</v>
+        <v>118.4557144990116</v>
       </c>
       <c r="D7" t="n">
-        <v>33.59638818703009</v>
+        <v>39.16584291322225</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C8" t="n">
-        <v>22.1138670381594</v>
+        <v>48.65050748395068</v>
       </c>
       <c r="D8" t="n">
-        <v>32.46148784092078</v>
+        <v>38.38633523605029</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>31.61718481526852</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>39.38280915586078</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>24.91184799526281</v>
+        <v>33.73775985644164</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
-        <v>34.82848155585983</v>
+        <v>45.84565429291754</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>22.34752299177014</v>
+        <v>33.1958351236974</v>
       </c>
       <c r="D12" t="n">
-        <v>33.41280136633594</v>
+        <v>44.91201222617883</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>32.5203927031756</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>42.66675522656638</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>31.03599017435442</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>28.66703296400686</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>41.20885988575986</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>16.13993225781756</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.296130138567888</v>
+        <v>17.69962461056944</v>
       </c>
       <c r="C21" t="n">
-        <v>77.5213827222838</v>
+        <v>126.5523159655715</v>
       </c>
       <c r="D21" t="n">
-        <v>6.384113871246902</v>
+        <v>5.309887383170833</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.220132469929538</v>
+        <v>1.0465430527271</v>
       </c>
       <c r="C2" t="n">
-        <v>11.88896469842888</v>
+        <v>7.072510461394022</v>
       </c>
       <c r="D2" t="n">
-        <v>23.81719930502762</v>
+        <v>24.11172361630166</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.69109363052752</v>
+        <v>8.51666133434108</v>
       </c>
       <c r="C3" t="n">
-        <v>36.8597175559465</v>
+        <v>36.62409810692726</v>
       </c>
       <c r="D3" t="n">
-        <v>53.39234889546279</v>
+        <v>64.64808632465245</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.72736154232243</v>
+        <v>9.023243149732433</v>
       </c>
       <c r="C4" t="n">
-        <v>68.16568834896879</v>
+        <v>93.37206065550565</v>
       </c>
       <c r="D4" t="n">
-        <v>61.23553130469055</v>
+        <v>57.80235958293945</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.21390749300135</v>
+        <v>8.320311793491719</v>
       </c>
       <c r="C5" t="n">
-        <v>93.24148821084083</v>
+        <v>101.9054117008189</v>
       </c>
       <c r="D5" t="n">
-        <v>44.22773407631881</v>
+        <v>37.3064127613788</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.77364255314227</v>
+        <v>5.152211951887262</v>
       </c>
       <c r="C6" t="n">
-        <v>100.3473780941792</v>
+        <v>78.00770908404307</v>
       </c>
       <c r="D6" t="n">
-        <v>36.50825187782615</v>
+        <v>25.76105975943631</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.34904451882213</v>
+        <v>5.030475236560656</v>
       </c>
       <c r="C7" t="n">
-        <v>72.16336500066178</v>
+        <v>34.19525428662065</v>
       </c>
       <c r="D7" t="n">
-        <v>35.51275970571987</v>
+        <v>26.94897448157494</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>38.38633523605029</v>
+        <v>23.28214680621311</v>
       </c>
       <c r="D8" t="n">
-        <v>34.63115026730623</v>
+        <v>28.95664853675967</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>26.29218526743382</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>33.83593462686631</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>26.1930287493049</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>35.87306111317846</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>26.4698816019025</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>34.60169783617884</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>34.41614752007619</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>32.25041208450772</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>30.17205219461722</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>30.69237847786803</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>13.84166088217578</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>96.16709636949629</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.510409514005654</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>87.30851060031573</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.510409514005654</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
